--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:07 PDT</t>
+          <t>2026-07-29 20:35 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:01 PDT</t>
+          <t>2026-07-29 20:12 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:07 PDT</t>
+          <t>2026-07-29 20:34 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,161 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:07 PDT</t>
+          <t>2026-07-29 20:35 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>generator/sim_utils.py</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Shared weighted date/channel sampling helpers</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_anonymous_population.py</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Phase 0 Step 4: builds the ~2,000-person anonymous ghost population</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>generator/simulate_customers.py</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Phase 0 Steps 5-6: per-customer master timeline + attribution ground truth</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>internal/_sim_anonymous_population.csv</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Internal artifact</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous visitors who never become tracked customers; source of guest merch orders</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>internal/_sim_customer_timeline.json</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Internal artifact</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Full nested ground-truth simulation for all 100 customers (signup, trial, subscriptions, orders, churn)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>internal/_sim_customer_timeline_summary.csv</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Internal artifact</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Flattened, spreadsheet-readable summary of the customer timeline</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>internal/_sim_attribution_ground_truth.json</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Internal artifact</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>True acquisition/reactivation channel per customer, kept separate from intentionally messy shipped UTM data</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 20:12 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:35 PDT</t>
+          <t>2026-07-29 21:16 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:12 PDT</t>
+          <t>2026-07-29 21:12 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:34 PDT</t>
+          <t>2026-07-29 21:15 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:35 PDT</t>
+          <t>2026-07-29 21:16 PDT</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:12 PDT</t>
+          <t>2026-07-29 21:12 PDT</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:11 PDT</t>
+          <t>2026-07-29 21:13 PDT</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:12 PDT</t>
+          <t>2026-07-29 21:12 PDT</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:12 PDT</t>
+          <t>2026-07-29 21:12 PDT</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,95 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:12 PDT</t>
+          <t>2026-07-29 21:12 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_simulation_charts.py</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Builds the funnel + segment breakdown charts for the simulation analysis</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>internal/funnel_chart.png</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Customer funnel: total -&gt; trial started -&gt; converted -&gt; active today</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>internal/segment_breakdown_chart.png</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Part-to-whole breakdown of all customers' current status</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>docs/phase0_simulation_analysis.md</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Summary analysis of the recalibrated Phase 0 simulation results</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:15 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:16 PDT</t>
+          <t>2026-07-29 21:38 PDT</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 19:56 PDT</t>
+          <t>2026-07-29 21:38 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:12 PDT</t>
+          <t>2026-07-29 21:34 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:16 PDT</t>
+          <t>2026-07-29 21:38 PDT</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:11 PDT</t>
+          <t>2026-07-29 21:33 PDT</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:12 PDT</t>
+          <t>2026-07-29 21:37 PDT</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:13 PDT</t>
+          <t>2026-07-29 21:35 PDT</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:12 PDT</t>
+          <t>2026-07-29 21:36 PDT</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:12 PDT</t>
+          <t>2026-07-29 21:36 PDT</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:12 PDT</t>
+          <t>2026-07-29 21:36 PDT</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:14 PDT</t>
+          <t>2026-07-29 21:35 PDT</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:14 PDT</t>
+          <t>2026-07-29 21:36 PDT</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:14 PDT</t>
+          <t>2026-07-29 21:36 PDT</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:15 PDT</t>
+          <t>2026-07-29 21:38 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:15 PDT</t>
+          <t>2026-07-29 21:55 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:38 PDT</t>
+          <t>2026-07-29 21:55 PDT</t>
         </is>
       </c>
     </row>
@@ -991,6 +991,72 @@
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 21:38 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_products.py</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds the products table (~12-item course/merch catalog)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_products.py</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for products (structural/referential/temporal/business-rule/distributional)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>data/products.csv</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: products table (course + merch catalog)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:55 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:38 PDT</t>
+          <t>2026-07-29 21:56 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:55 PDT</t>
+          <t>2026-07-29 21:58 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:55 PDT</t>
+          <t>2026-07-29 21:58 PDT</t>
         </is>
       </c>
     </row>
@@ -1057,6 +1057,72 @@
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 21:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_product_variants.py</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds product_variants (sizes for apparel, single variant elsewhere)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_product_variants.py</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for product_variants, including FK to products</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>data/product_variants.csv</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: product_variants table (21 variants across 12 products)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:57 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:56 PDT</t>
+          <t>2026-07-29 21:58 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:34 PDT</t>
+          <t>2026-07-29 21:59 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:58 PDT</t>
+          <t>2026-07-29 22:00 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:58 PDT</t>
+          <t>2026-07-29 22:00 PDT</t>
         </is>
       </c>
     </row>
@@ -1123,6 +1123,72 @@
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 21:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_subscription_plans.py</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds subscription_plans (Basic/Plus x monthly/annual)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_subscription_plans.py</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for subscription_plans</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>data/subscription_plans.csv</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: subscription_plans table (4 plans)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:58 PDT</t>
+          <t>2026-07-29 22:00 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:59 PDT</t>
+          <t>2026-07-29 22:02 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00 PDT</t>
+          <t>2026-07-29 22:02 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00 PDT</t>
+          <t>2026-07-29 22:02 PDT</t>
         </is>
       </c>
     </row>
@@ -1189,6 +1189,72 @@
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 22:00 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_customers.py</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds customers table from the master timeline; defines customer_id mapping</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_customers.py</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for customers, incl. 1:1 reconciliation vs. the timeline</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>data/customers.csv</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: customers table (860 rows, one per simulated customer)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:02 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00 PDT</t>
+          <t>2026-07-29 22:06 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:06 PDT</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:05 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:06 PDT</t>
+          <t>2026-07-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:06 PDT</t>
+          <t>2026-07-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:05 PDT</t>
+          <t>2026-07-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:05 PDT</t>
+          <t>2026-07-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:05 PDT</t>
+          <t>2026-07-29 22:07 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:07 PDT</t>
+          <t>2026-07-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -1255,6 +1255,72 @@
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 22:07 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_customer_addresses.py</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds customer_addresses (billing/shipping, obviously-fake streets)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:10 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_customer_addresses.py</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for customer_addresses</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>data/customer_addresses.csv</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: customer_addresses table (1,431 rows)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:10 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:07 PDT</t>
+          <t>2026-07-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:02 PDT</t>
+          <t>2026-07-29 22:13 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:11 PDT</t>
+          <t>2026-07-29 22:16 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:11 PDT</t>
+          <t>2026-07-29 22:16 PDT</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:11 PDT</t>
+          <t>2026-07-29 22:14 PDT</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:35 PDT</t>
+          <t>2026-07-29 22:15 PDT</t>
         </is>
       </c>
     </row>
@@ -1321,6 +1321,72 @@
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 22:10 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_devices.py</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds devices (customer + anonymous-ghost devices)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_devices.py</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for devices</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>data/devices.csv</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: devices table (18,042 rows: known-customer + ghost devices)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:15 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:11 PDT</t>
+          <t>2026-07-29 22:17 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:16 PDT</t>
+          <t>2026-07-29 22:22 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:16 PDT</t>
+          <t>2026-07-29 22:22 PDT</t>
         </is>
       </c>
     </row>
@@ -1387,6 +1387,72 @@
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 22:15 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_identity_map.py</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds identity_map (anonymous_id -&gt; customer_id resolution events)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:21 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_identity_map.py</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for identity_map</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:22 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>data/identity_map.csv</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: identity_map table (992 rows) -- last Phase 1 table</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:21 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:17 PDT</t>
+          <t>2026-07-29 22:22 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:22 PDT</t>
+          <t>2026-07-29 22:33 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:22 PDT</t>
+          <t>2026-07-29 22:33 PDT</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,78 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Phase 1: identity_map table (992 rows) -- last Phase 1 table</t>
+          <t>Phase 1: identity_map table (992 rows)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2026-07-29 22:21 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_segments.py</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: builds segments (10 definitions: 7 customer-grain, 3 anonymous)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_segments.py</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 5-layer validation for segments</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>data/segments.csv</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: segments table (10 rows) -- completes Phase 1 (all 8 tables)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:33 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:22 PDT</t>
+          <t>2026-07-29 22:36 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:33 PDT</t>
+          <t>2026-07-29 22:36 PDT</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:32 PDT</t>
+          <t>2026-07-29 22:36 PDT</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:33 PDT</t>
+          <t>2026-07-29 22:36 PDT</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:33 PDT</t>
+          <t>2026-07-29 22:36 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:36 PDT</t>
+          <t>2026-07-29 22:42 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:36 PDT</t>
+          <t>2026-07-29 22:42 PDT</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:36 PDT</t>
+          <t>2026-07-29 22:41 PDT</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:36 PDT</t>
+          <t>2026-07-29 22:41 PDT</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:36 PDT</t>
+          <t>2026-07-29 22:41 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:38 PDT</t>
+          <t>2026-07-29 22:45 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:42 PDT</t>
+          <t>2026-07-29 22:45 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:42 PDT</t>
+          <t>2026-07-29 22:54 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:33 PDT</t>
+          <t>2026-07-29 22:54 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:45 PDT</t>
+          <t>2026-07-29 22:54 PDT</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Phase 1: builds segments (10 definitions: 7 customer-grain, 3 anonymous)</t>
+          <t>Phase 1: builds segments (27 definitions: 9 customer-grain, 18 anonymous -- 3 audience concepts x 6 ad platforms)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:41 PDT</t>
+          <t>2026-07-29 22:53 PDT</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:41 PDT</t>
+          <t>2026-07-29 22:53 PDT</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Phase 1: segments table (10 rows) -- completes Phase 1 (all 8 tables)</t>
+          <t>Phase 1: segments table (27 rows) -- completes Phase 1 (all 8 tables)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:41 PDT</t>
+          <t>2026-07-29 22:54 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:54 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:45 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:13 PDT</t>
+          <t>2026-07-29 22:59 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:54 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:54 PDT</t>
+          <t>2026-07-29 23:04 PDT</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:53 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:53 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,73 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:54 PDT</t>
+          <t>2026-07-29 23:03 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_subscriptions.py</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: builds subscriptions (Stripe-shaped subscription objects; assigns billing_interval + next-renewal date, resolving the long-flagged Phase 2 gap)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_subscriptions.py</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: 5-layer validation for subscriptions</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>data/subscriptions.csv</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: subscriptions table (576 rows: one Stripe-shaped subscription object per trial-or-interval)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:02 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-07-30 10:34 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:59 PDT</t>
+          <t>2026-07-30 10:31 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-07-30 10:33 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:04 PDT</t>
+          <t>2026-07-30 10:34 PDT</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:02 PDT</t>
+          <t>2026-07-30 10:29 PDT</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:02 PDT</t>
+          <t>2026-07-30 10:30 PDT</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,73 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:02 PDT</t>
+          <t>2026-07-30 10:30 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_subscription_events.py</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: builds subscription_events (event log behind every subscription: trial_started/converted/expired, renewed, upgraded/downgraded, payment_failed, canceled, resumed)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_subscription_events.py</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: 5-layer validation for subscription_events</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>data/subscription_events.csv</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: subscription_events table (2,424 rows, incl. ~3% deliberate duplicate webhook-style rows)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:32 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:34 PDT</t>
+          <t>2026-07-30 11:29 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:33 PDT</t>
+          <t>2026-07-30 11:28 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:34 PDT</t>
+          <t>2026-07-30 11:29 PDT</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:32 PDT</t>
+          <t>2026-07-30 11:28 PDT</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:33 PDT</t>
+          <t>2026-07-30 11:27 PDT</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,78 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Phase 2: subscription_events table (2,424 rows, incl. ~3% deliberate duplicate webhook-style rows)</t>
+          <t>Phase 2: subscription_events table (2,423 rows, incl. ~3% deliberate duplicate webhook-style rows)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:32 PDT</t>
+          <t>2026-07-30 11:28 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_invoices.py</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: builds invoices (one per initial charge + renewal, plus uncollectible/open for failed payments) -- completes Phase 2 (all 3 tables)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:28 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_invoices.py</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: 5-layer validation for invoices</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:28 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>data/invoices.csv</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2: invoices table (1,229 rows) -- completes Phase 2</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:28 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:29 PDT</t>
+          <t>2026-07-30 13:06 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-07-30 13:06 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:29 PDT</t>
+          <t>2026-07-30 13:06 PDT</t>
         </is>
       </c>
     </row>
@@ -1717,6 +1717,72 @@
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 11:28 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_discount_codes.py</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: builds discount_codes (hand-curated list: evergreen + seasonal promo codes) -- built first in Phase 3 since orders needs it</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_discount_codes.py</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: 5-layer validation for discount_codes</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:06 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>data/discount_codes.csv</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: discount_codes table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:05 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:06 PDT</t>
+          <t>2026-07-30 13:22 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:31 PDT</t>
+          <t>2026-07-30 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:06 PDT</t>
+          <t>2026-07-30 13:22 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:06 PDT</t>
+          <t>2026-07-30 13:23 PDT</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Phase 0 Step 4: builds the ~2,000-person anonymous ghost population</t>
+          <t>Phase 0 Step 4: builds the ~2,000-person anonymous ghost population (anon_id now hash-derived, not uuid4 -- reproducibility fix)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:14 PDT</t>
+          <t>2026-07-30 13:20 PDT</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Phase 0 Steps 5-6: per-customer master timeline + attribution ground truth</t>
+          <t>Phase 0 Steps 5-6: per-customer master timeline + attribution ground truth (fixed: course_merch_only orders now reconciled against the eventual subscription window; pre_signup_anon_id now hash-derived, not uuid4)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:37 PDT</t>
+          <t>2026-07-30 13:20 PDT</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:36 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:36 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:36 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Phase 1: builds devices (customer + anonymous-ghost devices)</t>
+          <t>Phase 1: builds devices (customer + anonymous-ghost devices; 2nd-device anon_id now hash-derived, not uuid4)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:14 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:15 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:21 PDT</t>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1783,72 @@
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 13:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_orders.py</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: builds orders (customer course/merch + guest merch), cross-validated against subscriptions.csv</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:15 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_orders.py</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: 5-layer validation for orders, incl. the no-course-during-subscription cross-check</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>data/orders.csv</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: orders table (3,650 rows: 1,061 course + 1,332 customer-merch + 1,257 guest-merch)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:21 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:22 PDT</t>
+          <t>2026-07-30 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:23 PDT</t>
+          <t>2026-07-30 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -1849,6 +1849,72 @@
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 13:21 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_order_line_items.py</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: builds order_line_items (one row per order -- resolves each order's price tier down to a specific product + variant)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:39 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_order_line_items.py</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: 5-layer validation for order_line_items</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:40 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>data/order_line_items.csv</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: order_line_items table (3,650 rows, one per order)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:39 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:22 PDT</t>
+          <t>2026-07-30 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:15 PDT</t>
+          <t>2026-07-30 13:45 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:42 PDT</t>
+          <t>2026-07-30 13:46 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:42 PDT</t>
+          <t>2026-07-30 13:46 PDT</t>
         </is>
       </c>
     </row>
@@ -1915,6 +1915,72 @@
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 13:39 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_payments.py</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: builds payments (one Stripe-shaped Charge attempt per row; models realistic declined-then-retried charge attempts)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:45 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_payments.py</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: 5-layer validation for payments</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:46 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>data/payments.csv</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: payments table (3,964 rows: 3,650 succeeded + 314 failed retry attempts)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 13:45 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:42 PDT</t>
+          <t>2026-07-30 13:46 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:46 PDT</t>
+          <t>2026-07-30 17:51 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:46 PDT</t>
+          <t>2026-07-30 17:51 PDT</t>
         </is>
       </c>
     </row>
@@ -1981,6 +1981,72 @@
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 13:45 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_refunds.py</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: builds refunds (against a small share of orders' succeeded payments) -- completes Phase 3 (all 5 tables)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:50 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_refunds.py</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: 5-layer validation for refunds</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:51 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>data/refunds.csv</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Phase 3: refunds table (159 rows, 4.4% of orders) -- completes Phase 3</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 17:50 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:46 PDT</t>
+          <t>2026-07-30 17:51 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:51 PDT</t>
+          <t>2026-08-13 07:02 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:51 PDT</t>
+          <t>2026-08-13 07:02 PDT</t>
         </is>
       </c>
     </row>
@@ -2047,6 +2047,72 @@
       <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2026-07-30 17:50 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_customer_segment_membership.py</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4: builds customer_segment_membership (effective-dated, derived entirely from subscriptions/orders/invoices -- seg_009 skipped, needs Phase 5) -- completes Phase 4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:00 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_customer_segment_membership.py</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4: 5-layer validation for customer_segment_membership</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:01 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>data/customer_segment_membership.csv</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4: customer_segment_membership table (2,234 rows across 8 of 9 customer-grain segments) -- completes Phase 4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:00 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:51 PDT</t>
+          <t>2026-08-13 07:02 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:02 PDT</t>
+          <t>2026-08-13 07:11 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:02 PDT</t>
+          <t>2026-08-13 07:11 PDT</t>
         </is>
       </c>
     </row>
@@ -2113,6 +2113,72 @@
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:00 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_web_sessions.py</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: builds web_sessions (marketing-site browsing; known customers + anonymous ghosts, engagement_tier-driven volume)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_web_sessions.py</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: 5-layer validation for web_sessions</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>data/web_sessions.csv</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: web_sessions table (30,285 rows: 6,476 identity-resolved + 23,809 anonymous)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:11 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:02 PDT</t>
+          <t>2026-08-13 07:11 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-08-13 07:21 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-08-13 07:21 PDT</t>
         </is>
       </c>
     </row>
@@ -2179,6 +2179,72 @@
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:11 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_web_events.py</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: builds web_events (page_view/product_view/add_to_cart/begin_checkout/purchase/search; every order gets exactly one purchase event)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_web_events.py</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: 5-layer validation for web_events</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:21 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>data/web_events.csv</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: web_events table (117,706 rows)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:19 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-08-13 07:21 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:21 PDT</t>
+          <t>2026-08-13 07:34 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:21 PDT</t>
+          <t>2026-08-13 07:34 PDT</t>
         </is>
       </c>
     </row>
@@ -2245,6 +2245,72 @@
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_app_sessions.py</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: builds app_sessions (in-app fitness usage, driven by real subscription intervals + course orders, keyed off engagement_tier)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_app_sessions.py</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: 5-layer validation for app_sessions</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>data/app_sessions.csv</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: app_sessions table (19,610 rows across 496 customers)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:33 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:21 PDT</t>
+          <t>2026-08-13 07:35 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:34 PDT</t>
+          <t>2026-08-13 07:44 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:34 PDT</t>
+          <t>2026-08-13 07:44 PDT</t>
         </is>
       </c>
     </row>
@@ -2311,6 +2311,72 @@
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_app_events.py</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: builds app_events (class_started/workout_completed/workout_abandoned/streak_achieved -- streaks derived from real consecutive session dates) -- completes Phase 5</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:44 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_app_events.py</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: 5-layer validation for app_events</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:43 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>data/app_events.csv</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: app_events table (39,370 rows) -- completes Phase 5</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:44 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:35 PDT</t>
+          <t>2026-08-13 07:44 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:44 PDT</t>
+          <t>2026-08-13 07:49 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:44 PDT</t>
+          <t>2026-08-13 07:49 PDT</t>
         </is>
       </c>
     </row>
@@ -2377,6 +2377,72 @@
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:44 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_braze_email_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: builds braze_email_campaigns (hand-curated: 7 triggered + 2 broadcast) -- built first, events table needs it</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_braze_email_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: 5-layer validation for braze_email_campaigns</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:49 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>data/braze_email_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: braze_email_campaigns table (9 rows)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:48 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:44 PDT</t>
+          <t>2026-08-13 07:49 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:49 PDT</t>
+          <t>2026-08-13 07:57 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:49 PDT</t>
+          <t>2026-08-13 07:58 PDT</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:19 PDT</t>
+          <t>2026-08-13 07:57 PDT</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:19 PDT</t>
+          <t>2026-08-13 07:57 PDT</t>
         </is>
       </c>
     </row>
@@ -2443,6 +2443,116 @@
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_web_events.py</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: builds web_events (retroactive fix: timestamp offsets now rounded to whole seconds, fixing a latent fractional-second formatting bug across all 117,706 rows)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>data/web_events.csv</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5: web_events table (117,706 rows; retroactively rebuilt for the whole-second timestamp fix, same counts/logic)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_braze_email_events.py</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: builds braze_email_events (Send/Open/Click/Bounce/Unsubscribe funnel, derived from real trial/payment-failure/order/cart/reactivation sources)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_braze_email_events.py</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: 5-layer validation for braze_email_events</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>data/braze_email_events.csv</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: braze_email_events table (26,328 rows, 18,187 sends)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:57 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:49 PDT</t>
+          <t>2026-08-13 07:58 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-08-13 08:00 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:58 PDT</t>
+          <t>2026-08-13 08:00 PDT</t>
         </is>
       </c>
     </row>
@@ -2553,6 +2553,72 @@
       <c r="D96" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_braze_push_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: builds braze_push_campaigns (hand-curated: 5 triggered + 2 broadcast, push-appropriate subset) -- built before events table needs it</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_braze_push_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: 5-layer validation for braze_push_campaigns</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:00 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>data/braze_push_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: braze_push_campaigns table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 07:59 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:58 PDT</t>
+          <t>2026-08-13 08:00 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:00 PDT</t>
+          <t>2026-08-13 08:07 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:00 PDT</t>
+          <t>2026-08-13 08:07 PDT</t>
         </is>
       </c>
     </row>
@@ -2619,6 +2619,72 @@
       <c r="D99" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 07:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_braze_push_events.py</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: builds braze_push_events (Send/Open/Click/Bounce/Unsubscribe funnel, gated on push_opt_in as a hard delivery precondition) -- completes Phase 6 (all 4 tables)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:03 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_braze_push_events.py</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: 5-layer validation for braze_push_events</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:06 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>data/braze_push_events.csv</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Phase 6: braze_push_events table (9,897 rows, 7,851 sends) -- completes Phase 6 (25 of 47 tables shipped; Phase 7 paid media remains)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:05 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:00 PDT</t>
+          <t>2026-08-13 08:08 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:45 PDT</t>
+          <t>2026-08-13 10:57 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:07 PDT</t>
+          <t>2026-08-13 10:59 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:07 PDT</t>
+          <t>2026-08-13 10:59 PDT</t>
         </is>
       </c>
     </row>
@@ -2685,6 +2685,292 @@
       <c r="D102" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 08:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>generator/paid_media_common.py</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: shared helpers used by all 6 platforms' daily performance tables -- maps any date to the seasonality calendar/channel-mix week and draws each day's per-channel spend baseline</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:54 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_meta_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 1/4): builds meta_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns timed near BFCM)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_meta_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for meta_campaigns</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 1/4): meta_campaigns table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_meta_ads.py</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 2/4): builds meta_ads (functions as the ad-set-level entity -- targeting_segment_id for retargeting/lookalike only)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_meta_ads.py</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for meta_ads</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_ads.csv</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 2/4): meta_ads table (10 rows)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_meta_ad_insights_daily.py</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 3/4): builds meta_ad_insights_daily (spend/impressions/clicks driven by the shared seasonality calendar + channel-mix schedule)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_meta_ad_insights_daily.py</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for meta_ad_insights_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_ad_insights_daily.csv</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 3/4): meta_ad_insights_daily table (7,396 rows)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_meta_ad_actions_daily.py</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 4/4): builds meta_ad_actions_daily (normalized actions array, derived directly from meta_ad_insights_daily.csv's own clicks) -- completes Meta (1 of 6 platforms)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_meta_ad_actions_daily.py</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for meta_ad_actions_daily</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_ad_actions_daily.csv</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Meta 4/4): meta_ad_actions_daily table (35,504 rows) -- completes Meta</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:57 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:08 PDT</t>
+          <t>2026-08-13 10:59 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:57 PDT</t>
+          <t>2026-08-13 12:17 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:59 PDT</t>
+          <t>2026-08-13 12:19 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:59 PDT</t>
+          <t>2026-08-13 12:19 PDT</t>
         </is>
       </c>
     </row>
@@ -2971,6 +2971,270 @@
       <c r="D115" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 10:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_google_search_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 1/4): builds google_search_campaigns (5 evergreen objective campaigns, incl. an always-on brand-term defense campaign)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:16 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_google_search_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for google_search_campaigns</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:18 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>data/google_search_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 1/4): google_search_campaigns table (5 rows)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:16 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_google_search_ad_groups.py</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 2/4): builds google_search_ad_groups (targeting_segment_id for RLSA retargeting/similar-audience lookalike only)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:16 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_google_search_ad_groups.py</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for google_search_ad_groups</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:18 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>data/google_search_ad_groups.csv</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 2/4): google_search_ad_groups table (8 rows)</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:16 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_google_search_keyword_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 4/4 by build order): builds google_search_keyword_performance_daily -- the granular ground truth google_search_performance_daily aggregates from</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_google_search_keyword_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for google_search_keyword_performance_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:18 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>data/google_search_keyword_performance_daily.csv</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 4/4 by build order): google_search_keyword_performance_daily table (19,932 rows)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_google_search_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 3/4 by schema order): builds google_search_performance_daily, aggregated exactly from keyword_performance_daily.csv up to ad_group/day grain -- completes Google Search (2 of 6 platforms)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_google_search_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for google_search_performance_daily, incl. exact-sum reconciliation against keyword_performance_daily.csv</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>data/google_search_performance_daily.csv</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Google Search 3/4 by schema order): google_search_performance_daily table (8,751 rows) -- completes Google Search</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:59 PDT</t>
+          <t>2026-08-13 12:19 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:17 PDT</t>
+          <t>2026-08-13 12:29 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:19 PDT</t>
+          <t>2026-08-13 12:29 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:19 PDT</t>
+          <t>2026-08-13 12:29 PDT</t>
         </is>
       </c>
     </row>
@@ -3235,6 +3235,204 @@
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 12:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_youtube_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 1/3): builds youtube_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns, mirroring Meta's structure since YouTube Brand Lift is a real flighted measurement product)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:25 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_youtube_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for youtube_campaigns</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>data/youtube_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 1/3): youtube_campaigns table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_youtube_ad_groups.py</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 2/3): builds youtube_ad_groups (targeting_segment_id for retargeting/lookalike only)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:25 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_youtube_ad_groups.py</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for youtube_ad_groups</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:27 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>data/youtube_ad_groups.csv</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 2/3): youtube_ad_groups table (9 rows)</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_youtube_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 3/3): builds youtube_performance_daily (video_views/video_view_rate/average_cpv, spend-driven by the shared seasonality calendar + channel-mix schedule) -- completes YouTube (3 of 6 platforms)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_youtube_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for youtube_performance_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:27 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>data/youtube_performance_daily.csv</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (YouTube 3/3): youtube_performance_daily table (6,394 rows) -- completes YouTube</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:29 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:19 PDT</t>
+          <t>2026-08-13 12:29 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-08-13 12:32 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-08-13 12:34 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-08-13 12:34 PDT</t>
         </is>
       </c>
     </row>
@@ -3433,6 +3433,204 @@
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 12:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_dv360_insertion_orders.py</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 1/3): builds dv360_insertion_orders (5 evergreen objective IOs, incl. a VIEWABLE_CPM awareness IO)</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_dv360_insertion_orders.py</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for dv360_insertion_orders</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>data/dv360_insertion_orders.csv</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 1/3): dv360_insertion_orders table (5 rows)</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_dv360_line_items.py</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 2/3): builds dv360_line_items (targeting_segment_id for retargeting/lookalike only; brand_lift IO's line item is VIDEO type)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_dv360_line_items.py</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for dv360_line_items</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>data/dv360_line_items.csv</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 2/3): dv360_line_items table (6 rows)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:32 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_dv360_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 3/3): builds dv360_performance_daily -- fragments each line_item/day into several (exchange, environment) rows, DV360's genuinely different real-time-bidding schema shape -- completes DV360 (4 of 6 platforms)</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_dv360_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for dv360_performance_daily, incl. weekly-spend-vs-web_sessions correlation check and CONNECTED_TV-only-on-video-line-item check</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>data/dv360_performance_daily.csv</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (DV360 3/3): dv360_performance_daily table (25,776 rows) -- completes DV360</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:33 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-08-13 12:34 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:32 PDT</t>
+          <t>2026-08-13 12:46 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:34 PDT</t>
+          <t>2026-08-13 12:48 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:34 PDT</t>
+          <t>2026-08-13 12:48 PDT</t>
         </is>
       </c>
     </row>
@@ -3631,6 +3631,270 @@
       <c r="D145" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 12:33 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_snap_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 1/4): builds snap_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns, flight budgets calibrated to avoid YouTube's earlier scale bug)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:46 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_snap_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for snap_campaigns</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 1/4): snap_campaigns table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:46 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_snap_ad_squads.py</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 2/4): builds snap_ad_squads (Snap's own real ad-set-level targeting entity, unlike Meta -- targeting_segment_id for retargeting/lookalike only)</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:46 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_snap_ad_squads.py</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for snap_ad_squads</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_ad_squads.csv</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 2/4): snap_ad_squads table (8 rows)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:46 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_snap_ads.py</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 3/4): builds snap_ads (creative-level entity, no targeting -- that lives on the ad squad)</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_snap_ads.py</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for snap_ads</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_ads.csv</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 3/4): snap_ads table (10 rows)</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_snap_stats_daily.py</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 4/4): builds snap_stats_daily (spend in Snap's own micro-currency unit, swipes as the click-equivalent) -- completes Snap (5 of 6 platforms)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_snap_stats_daily.py</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for snap_stats_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_stats_daily.csv</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (Snap 4/4): snap_stats_daily table (7,407 rows) -- completes Snap</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:47 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:34 PDT</t>
+          <t>2026-08-13 12:49 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:48 PDT</t>
+          <t>2026-08-13 14:38 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:48 PDT</t>
+          <t>2026-08-13 14:38 PDT</t>
         </is>
       </c>
     </row>
@@ -3895,6 +3895,270 @@
       <c r="D157" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 12:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_tiktok_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 1/4): builds tiktok_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns)</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_tiktok_campaigns.py</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for tiktok_campaigns</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:36 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 1/4): tiktok_campaigns table (7 rows)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_tiktok_adgroups.py</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 2/4): builds tiktok_adgroups (TikTok's own real ad-set-level targeting entity -- targeting_segment_id for retargeting/lookalike only)</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_tiktok_adgroups.py</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for tiktok_adgroups</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:36 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_adgroups.csv</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 2/4): tiktok_adgroups table (8 rows)</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:34 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_tiktok_ads.py</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 3/4): builds tiktok_ads (creative-level entity, no targeting -- that lives on the ad group)</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:35 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_tiktok_ads.py</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for tiktok_ads</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:36 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_ads.csv</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 3/4): tiktok_ads table (10 rows)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:35 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_tiktok_reports_daily.py</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 4/4): builds tiktok_reports_daily (spend/impressions/video_views, TikTok's always-video ad format) -- completes TikTok (6 of 6 platforms) AND all 47 tables</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:35 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>generator/validate_tiktok_reports_daily.py</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7: 5-layer validation for tiktok_reports_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:36 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_reports_daily.csv</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7 (TikTok 4/4): tiktok_reports_daily table (7,416 rows) -- completes TikTok, Phase 7, and the full 47-table dataset</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:35 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:49 PDT</t>
+          <t>2026-08-13 15:13 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:38 PDT</t>
+          <t>2026-08-13 15:15 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:38 PDT</t>
+          <t>2026-08-13 15:15 PDT</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:55 PDT</t>
+          <t>2026-08-13 15:11 PDT</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Phase 6: braze_email_events table (26,328 rows, 18,187 sends)</t>
+          <t>Phase 6: braze_email_events table (26,335 rows, 18,187 sends) -- updated 2026-08-13 by the cross-dataset audit's Check 6 fix (merch_to_sub_trigger send time-of-day)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-08-13 15:11 PDT</t>
         </is>
       </c>
     </row>
@@ -4159,6 +4159,50 @@
       <c r="D169" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 14:35 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>generator/audit_cross_dataset_alignment.py</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Post-completion cross-dataset alignment audit -- NOT a shipped-table script. 7 checks: aggregate spend vs. demand, channel mix vs. schedule, calendar-event alignment, long-run growth trend, renewal/lag structure, day-of-week/hour-of-day, timezone/precision sweep. Found and fixed a real bug (Check 6 -- merch_to_sub_trigger Braze sends all landing at exactly midnight); Checks 3 and 5 surfaced genuine, documented (non-bug) characteristics.</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 15:12 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>docs/cross_dataset_alignment_audit.md</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Write-up of the 7-check cross-dataset alignment audit's results, including the merch_to_sub_trigger bug fix and the two documented (non-bug) findings from Checks 3 and 5</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 15:14 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:15 PDT</t>
+          <t>2026-08-13 15:37 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:15 PDT</t>
+          <t>2026-08-13 15:37 PDT</t>
         </is>
       </c>
     </row>
@@ -4203,6 +4203,28 @@
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 15:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>warehouse/load_to_motherduck.py</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have).</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 15:37 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:13 PDT</t>
+          <t>2026-08-13 15:37 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:37 PDT</t>
+          <t>2026-08-13 15:45 PDT</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:06 PDT</t>
+          <t>2026-08-13 15:44 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:37 PDT</t>
+          <t>2026-08-13 15:45 PDT</t>
         </is>
       </c>
     </row>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have).</t>
+          <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have). Reads its motherduck_token from either a shell env var or an optional warehouse/.env file (gitignored -- NOT tracked or synced by this manifest, since it holds a live credential).</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:37 PDT</t>
+          <t>2026-08-13 15:45 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:37 PDT</t>
+          <t>2026-08-13 15:56 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:45 PDT</t>
+          <t>2026-08-13 15:56 PDT</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:45 PDT</t>
+          <t>2026-08-13 15:56 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:56 PDT</t>
+          <t>2026-08-14 10:16 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:45 PDT</t>
+          <t>2026-08-14 10:16 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:56 PDT</t>
+          <t>2026-08-14 10:17 PDT</t>
         </is>
       </c>
     </row>
@@ -4219,12 +4219,34 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have). Reads its motherduck_token from either a shell env var or an optional warehouse/.env file (gitignored -- NOT tracked or synced by this manifest, since it holds a live credential).</t>
+          <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have). Reads its motherduck_token from either a shell env var or an optional warehouse/.env file (gitignored -- NOT tracked or synced by this manifest, since it holds a live credential). Confirmed working end-to-end against the user's own MotherDuck account (47/47 tables, exact row-count match).</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
           <t>2026-08-13 15:56 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>warehouse/analysis_queries.sql</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>6 starter SQL queries against the kinetic MotherDuck database: monthly paid media spend by partner, directly attributed revenue by paid/owned channel, active subscribers by month, non-subscription revenue by month, monthly churn rate, top 5 grossing products per year. Heavily commented to explain modeling choices (e.g. the paid/owned attribution methodology split between storefront orders and subscription invoices).</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:16 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:16 PDT</t>
+          <t>2026-08-14 10:56 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:17 PDT</t>
+          <t>2026-08-14 10:56 PDT</t>
         </is>
       </c>
     </row>
@@ -4247,6 +4247,28 @@
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t>2026-08-14 10:16 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>warehouse/query1_paid_media_spend.html</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>One-off interactive chart visualizing Query 1's actual output (pasted by the user from their own MotherDuck run): monthly paid media spend by partner, Aug 2023-Jul 2026. Multi-line chart with hover tooltip, legend isolate-toggle, dark mode, and a table view -- built per the dataviz skill (validated categorical palette, accessible contrast handling).</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:55 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:16 PDT</t>
+          <t>2026-08-14 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:56 PDT</t>
+          <t>2026-08-14 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:56 PDT</t>
+          <t>2026-08-14 13:42 PDT</t>
         </is>
       </c>
     </row>
@@ -4269,6 +4269,28 @@
       <c r="D174" s="2" t="inlineStr">
         <is>
           <t>2026-08-14 10:55 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>warehouse/kinetic_dive.tsx</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Source for the 'Kinetic -- Marketing &amp; Revenue Overview' MotherDuck Dive -- a live, hosted interactive dashboard (React/Recharts) covering all 6 requested queries (spend by partner, attributed revenue by channel, active subscribers, non-subscription revenue, churn rate, top products by year) plus a KPI row. Re-runs the real SQL against the live kinetic database on every open, unlike the earlier static HTML chart. Saved to MotherDuck via the MCP tools; this file is the local source-of-truth copy for sync/history. Live at https://app.motherduck.com/dives/kinetic-marketing-revenue-overview-58909b4e-d301-4794-bb59-ce46f9dc73a6 (dive_id 58909b4e-d301-4794-bb59-ce46f9dc73a6).</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:42 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 13:42 PDT</t>
+          <t>2026-08-14 14:17 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 13:42 PDT</t>
+          <t>2026-08-14 14:16 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 13:42 PDT</t>
+          <t>2026-08-14 14:17 PDT</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Source for the 'Kinetic -- Marketing &amp; Revenue Overview' MotherDuck Dive -- a live, hosted interactive dashboard (React/Recharts) covering all 6 requested queries (spend by partner, attributed revenue by channel, active subscribers, non-subscription revenue, churn rate, top products by year) plus a KPI row. Re-runs the real SQL against the live kinetic database on every open, unlike the earlier static HTML chart. Saved to MotherDuck via the MCP tools; this file is the local source-of-truth copy for sync/history. Live at https://app.motherduck.com/dives/kinetic-marketing-revenue-overview-58909b4e-d301-4794-bb59-ce46f9dc73a6 (dive_id 58909b4e-d301-4794-bb59-ce46f9dc73a6).</t>
+          <t>Source for the 'Kinetic -- Marketing &amp; Revenue Overview' MotherDuck Dive -- a live, hosted interactive dashboard (React/Recharts), now organized as 5 tabs. Overview tab: the original 6 starter queries + KPI row. CEO tab: revenue growth/net-new-vs-churned subscribers/CAC payback, revenue mix (subscription vs. course vs. merch). CMO tab: acquisition funnel by channel (sessions -&gt; trial starts -&gt; conversions), retention/app engagement by acquisition channel. CFO tab: CAC and LTV:CAC by acquisition cohort, discount code cost + failed-payment recovery rate + a documented net-margin proxy (no COGS data exists for a true gross margin). Performance Marketing tab: campaign-level spend and platform-self-reported efficiency across all 38 real campaigns (sorted worst-CAC-first), CTR/CVR by platform and ad format. Each new section documents its modeling limits explicitly (e.g. platform-reported vs. site-attributed conversions have no shared join key in this dataset). Re-runs live SQL against the kinetic database on every open. Saved to MotherDuck via the MCP tools; this file is the local source-of-truth copy for sync/history. Live at https://app.motherduck.com/dives/kinetic-marketing-revenue-overview-58909b4e-d301-4794-bb59-ce46f9dc73a6 (dive_id 58909b4e-d301-4794-bb59-ce46f9dc73a6, version 2).</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 13:42 PDT</t>
+          <t>2026-08-14 14:13 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 19:55 PDT</t>
+          <t>2026-09-28 14:47 PDT</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 14:17 PDT</t>
+          <t>2026-09-28 14:47 PDT</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 19:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 19:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:01 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 14:16 PDT</t>
+          <t>2026-09-28 14:49 PDT</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:01 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:01 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 20:01 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:44 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 14:17 PDT</t>
+          <t>2026-09-28 14:49 PDT</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:20 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:20 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:15 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:35 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:38 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 21:59 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:00 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:07 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:07 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:07 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:10 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:10 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:13 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 22:22 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 23:03 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:29 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:27 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:05 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:06 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:05 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:15 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:17 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:39 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:40 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:39 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:45 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 13:45 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:50 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:51 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30 17:50 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:00 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:01 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:00 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:21 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:44 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:43 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:44 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:48 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:49 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:48 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:11 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:59 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:00 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 07:59 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:03 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:06 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:05 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:54 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:58 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:58 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:59 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:57 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:16 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:18 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:16 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:16 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:18 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:16 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:17 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:18 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:17 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:17 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:19 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:17 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:25 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:26 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:25 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:27 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:26 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:27 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:29 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:32 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:32 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:32 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:32 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:33 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:47 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:48 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:46 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:47 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:48 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:47 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:47 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:48 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:47 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:34 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:35 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:35 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:35 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:36 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 14:35 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:12 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:14 PDT</t>
+          <t>2026-09-28 14:47 PDT</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:56 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:16 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:55 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,359 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 14:13 PDT</t>
+          <t>2026-09-28 14:09 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-28: real project status (47/47 tables built+validated, live in MotherDuck) + direct link to the live Dive dashboard, replacing the stale 'planning complete, next step Phase 0' placeholder text</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>docs/cross_dataset_alignment_audit.md</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-28: closed the one open item (brand_lift/holiday-discount-code asymmetry across the 3 Novembers) -- reviewed and confirmed intentional, no data changed</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:47 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>dbt/dbt_project.yml</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>dbt project config for the new semantic layer -- staging views, intermediate views, mart tables</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>dbt/.gitignore</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Repo config</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Excludes dbt's target/, dbt_packages/, logs/ from git</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>dbt/README.md</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>How to install dbt-core + dbt-duckdb and run this project locally against MotherDuck (neither of Claude's environments can reach motherduck.com directly, so dbt run/test must be executed on the user's own machine)</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__sources.yml</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Declares all 47 raw kinetic tables as dbt sources, so every staging model references source() rather than a hardcoded table name</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customers.sql</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of customers with light renaming</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_plans.sql</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of subscription_plans</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscriptions.sql</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of subscriptions</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__invoices.sql</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of invoices</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__products.sql</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of products</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>not_null/unique/relationships tests for the Phase 1/2 staging models</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/int_subscription_paid_periods.sql</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Intermediate model: resolves each subscription's true paid-start date (trial-vs-paid logic), defined once so every downstream mart agrees</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/_intermediate.yml</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Tests for int_subscription_paid_periods</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/mart_mrr_monthly.sql</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>First canonical metric mart: active subscribers + MRR/ARR by month, validated against a hand-run equivalent query on the live database (2026-07: 90 active subscribers, ~$2,133 MRR)</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/_marts.yml</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Tests for mart_mrr_monthly</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:48 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:49 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:49 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,183 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>dbt/README.md</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Updated: what's built so far now includes the Phase 3 storefront staging models + mart_storefront_revenue_monthly</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__orders.sql</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of orders, plus is_guest_order/has_discount convenience booleans</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__order_line_items.sql</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of order_line_items</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__payments.sql</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of payments</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__refunds.sql</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of refunds</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__discount_codes.sql</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Staging model: 1:1 pass-through of discount_codes</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/int_orders_refunded.sql</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Intermediate model: per-order total of succeeded refunds only (failed/pending refunds don't reduce reported revenue)</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:47 PDT</t>
+          <t>2026-09-29 10:27 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 10:27 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 10:27 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 10:27 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 10:27 PDT</t>
         </is>
       </c>
     </row>
@@ -4819,6 +4819,160 @@
       <c r="D199" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 14:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D206"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:27 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:27 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:27 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:27 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:27 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,117 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:58 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 13:00 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 13:00 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 13:00 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 13:00 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 13:00 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,117 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:59 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D216"/>
+  <dimension ref="A1:D221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00 PDT</t>
+          <t>2026-09-29 13:03 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00 PDT</t>
+          <t>2026-09-29 13:03 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00 PDT</t>
+          <t>2026-09-29 13:03 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00 PDT</t>
+          <t>2026-09-29 13:03 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00 PDT</t>
+          <t>2026-09-29 13:03 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,117 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:03 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:03 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:03 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:03 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:03 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,117 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D226"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:15 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,95 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D230"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:15 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,95 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:19 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:28 PDT</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,205 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>generator/params.py</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:23 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>data/google_search_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>data/youtube_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>data/dv360_insertion_orders.csv</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_campaigns.csv</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>generator/audit_cross_dataset_alignment.py</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:24 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D243"/>
+  <dimension ref="A1:D254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:28 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:47 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:47 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
@@ -5787,6 +5787,248 @@
       <c r="D243" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 13:27 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>generator/paid_media_common.py</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_meta_ad_insights_daily.py</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_snap_stats_daily.py</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_tiktok_reports_daily.py</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>generator/build_youtube_performance_daily.py</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_ad_insights_daily.csv</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>data/meta_ad_actions_daily.csv</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>data/snap_stats_daily.csv</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>data/tiktok_reports_daily.csv</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Shipped table</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:29 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>docs/cross_dataset_alignment_audit.md</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:54 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>generator/audit_cross_dataset_alignment.py</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D254"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
@@ -6029,6 +6029,116 @@
       <c r="D254" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 13:30 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:53 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D259"/>
+  <dimension ref="A1:D264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,117 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D264"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:09 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:09 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:09 PDT</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
@@ -6233,22 +6233,44 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:57 PDT</t>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:09 PDT</t>
+          <t>2026-09-29 16:18 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:09 PDT</t>
+          <t>2026-09-29 16:18 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:09 PDT</t>
+          <t>2026-09-29 16:18 PDT</t>
         </is>
       </c>
     </row>
@@ -6255,20 +6255,42 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:18 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:08 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18 PDT</t>
+          <t>2026-09-29 16:33 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18 PDT</t>
+          <t>2026-09-29 16:33 PDT</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18 PDT</t>
+          <t>2026-09-29 16:33 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:33 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:18 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:33 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:09 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Tests for int_subscription_paid_periods</t>
+          <t>Descriptions and tests for all intermediate models</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:09 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>dbt/models/intermediate/int_customer_identity.sql</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -4813,19 +4813,19 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Intermediate model: lookup from every web anonymous_id and account email to its customer (guest emails matched by email; anonymous sessions back-filled; deleted accounts excluded)</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -4835,19 +4835,19 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -4967,19 +4967,19 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -5099,19 +5099,19 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,19 +5297,19 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,19 +5407,19 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,19 +5495,19 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,19 +5583,19 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,41 +5605,41 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -5749,29 +5749,29 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -5903,17 +5903,17 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -5991,51 +5991,51 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -6045,19 +6045,19 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -6133,19 +6133,19 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -6155,19 +6155,19 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -6243,54 +6243,76 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:33 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:39 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:08 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:09 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
@@ -4363,73 +4363,73 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>dbt/.gitignore</t>
+          <t>dbt/profiles.yml</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Repo config</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Excludes dbt's target/, dbt_packages/, logs/ from git</t>
+          <t>dbt connection profile (MotherDuck md:kinetic, schema dbt_dev); no secrets</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>dbt/README.md</t>
+          <t>dbt/.gitignore</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Repo config</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>How to install dbt-core + dbt-duckdb and run this project locally against MotherDuck (neither of Claude's environments can reach motherduck.com directly, so dbt run/test must be executed on the user's own machine)</t>
+          <t>Excludes dbt's target/, dbt_packages/, logs/ from git</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-28 14:48 PDT</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__sources.yml</t>
+          <t>dbt/README.md</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Declares all 47 raw kinetic tables as dbt sources, so every staging model references source() rather than a hardcoded table name</t>
+          <t>How to install dbt-core + dbt-duckdb and run this project locally against MotherDuck (neither of Claude's environments can reach motherduck.com directly, so dbt run/test must be executed on the user's own machine)</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customers.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__sources.yml</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of customers with light renaming</t>
+          <t>Declares all 47 raw kinetic tables as dbt sources, so every staging model references source() rather than a hardcoded table name</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_plans.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customers.sql</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of subscription_plans</t>
+          <t>Staging model: 1:1 pass-through of customers with light renaming</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscriptions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_plans.sql</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of subscriptions</t>
+          <t>Staging model: 1:1 pass-through of subscription_plans</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__invoices.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscriptions.sql</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of invoices</t>
+          <t>Staging model: 1:1 pass-through of subscriptions</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__products.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__invoices.sql</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of products</t>
+          <t>Staging model: 1:1 pass-through of invoices</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__products.sql</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -4549,19 +4549,19 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>not_null/unique/relationships tests for the Phase 1/2 staging models</t>
+          <t>Staging model: 1:1 pass-through of products</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-28 14:48 PDT</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/intermediate/int_subscription_paid_periods.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -4571,19 +4571,19 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Intermediate model: resolves each subscription's true paid-start date (trial-vs-paid logic), defined once so every downstream mart agrees</t>
+          <t>not_null/unique/relationships tests for the Phase 1/2 staging models</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/intermediate/_intermediate.yml</t>
+          <t>dbt/models/intermediate/int_subscription_paid_periods.sql</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -4593,19 +4593,19 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Descriptions and tests for all intermediate models</t>
+          <t>Intermediate model: resolves each subscription's true paid-start date (trial-vs-paid logic), defined once so every downstream mart agrees</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-28 14:48 PDT</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_mrr_monthly.sql</t>
+          <t>dbt/models/intermediate/_intermediate.yml</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -4615,19 +4615,19 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>First canonical metric mart: active subscribers + MRR/ARR by month, validated against a hand-run equivalent query on the live database (2026-07: 90 active subscribers, ~$2,133 MRR)</t>
+          <t>Descriptions and tests for all intermediate models</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/_marts.yml</t>
+          <t>dbt/models/marts/mart_mrr_monthly.sql</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -4637,63 +4637,63 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Tests for mart_mrr_monthly</t>
+          <t>First canonical metric mart: active subscribers + MRR/ARR by month, validated against a hand-run equivalent query on the live database (2026-07: 90 active subscribers, ~$2,133 MRR)</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-28 14:48 PDT</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>dbt/README.md</t>
+          <t>dbt/models/marts/_marts.yml</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Updated: what's built so far now includes the Phase 3 storefront staging models + mart_storefront_revenue_monthly</t>
+          <t>Tests for mart_mrr_monthly</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__orders.sql</t>
+          <t>dbt/README.md</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of orders, plus is_guest_order/has_discount convenience booleans</t>
+          <t>Updated: what's built so far now includes the Phase 3 storefront staging models + mart_storefront_revenue_monthly</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 16:43 PDT</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__order_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__orders.sql</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of order_line_items</t>
+          <t>Staging model: 1:1 pass-through of orders, plus is_guest_order/has_discount convenience booleans</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__payments.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__order_line_items.sql</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of payments</t>
+          <t>Staging model: 1:1 pass-through of order_line_items</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__refunds.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__payments.sql</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of refunds</t>
+          <t>Staging model: 1:1 pass-through of payments</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__discount_codes.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__refunds.sql</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Staging model: 1:1 pass-through of discount_codes</t>
+          <t>Staging model: 1:1 pass-through of refunds</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/intermediate/int_orders_refunded.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__discount_codes.sql</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Intermediate model: per-order total of succeeded refunds only (failed/pending refunds don't reduce reported revenue)</t>
+          <t>Staging model: 1:1 pass-through of discount_codes</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/intermediate/int_customer_identity.sql</t>
+          <t>dbt/models/intermediate/int_orders_refunded.sql</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -4813,19 +4813,19 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Intermediate model: lookup from every web anonymous_id and account email to its customer (guest emails matched by email; anonymous sessions back-filled; deleted accounts excluded)</t>
+          <t>Intermediate model: per-order total of succeeded refunds only (failed/pending refunds don't reduce reported revenue)</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>dbt/models/intermediate/int_customer_identity.sql</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -4835,19 +4835,19 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Intermediate model: lookup from every web anonymous_id and account email to its customer (guest emails matched by email; anonymous sessions back-filled; deleted accounts excluded)</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 16:39 PDT</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -4857,19 +4857,19 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -5099,19 +5099,19 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,19 +5561,19 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,19 +5605,19 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -5627,41 +5627,41 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -5771,29 +5771,29 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -5825,19 +5825,19 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -6013,51 +6013,51 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -6067,19 +6067,19 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -6155,19 +6155,19 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -6177,19 +6177,19 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -6265,54 +6265,76 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:43 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:08 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 17:03 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 17:03 PDT</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:39 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:48 PDT</t>
+          <t>2026-09-29 17:02 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 17:02 PDT</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 17:03 PDT</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D268"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03 PDT</t>
+          <t>2026-09-29 17:09 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>dbt/models/intermediate/int_orders_net.sql</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -4857,19 +4857,19 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Intermediate model: one row per order with gross (pre-discount), discount, paid, succeeded-refund and net amounts, plus customer_id resolved for guest orders via email match</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>dbt/tests/assert_int_orders_net_no_negative_net.sql</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -4879,19 +4879,19 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>dbt test: fails if any order's net is below zero (net is deliberately not floored)</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>dbt/tests/assert_int_orders_net_money_reconciles.sql</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -4901,19 +4901,19 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>dbt test: gross - discount = paid and paid - refund = net on every order</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/tests/assert_int_orders_net_refunds_match_source.sql</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -4923,19 +4923,19 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>dbt test: total refunds in int_orders_net equal total succeeded refunds in int_orders_refunded</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:18 PDT</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -4945,19 +4945,19 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -5033,19 +5033,19 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -5055,19 +5055,19 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -5099,19 +5099,19 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,19 +5143,19 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,19 +5165,19 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,19 +5275,19 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,19 +5297,19 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,19 +5363,19 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,19 +5385,19 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,19 +5407,19 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,19 +5473,19 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,19 +5495,19 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,19 +5561,19 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,19 +5583,19 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5649,107 +5649,107 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -5793,95 +5793,95 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -5891,19 +5891,19 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -5913,19 +5913,19 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -5947,17 +5947,17 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -5969,17 +5969,17 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -5991,17 +5991,17 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -6013,17 +6013,17 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -6035,117 +6035,117 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -6155,19 +6155,19 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -6177,19 +6177,19 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -6199,19 +6199,19 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -6221,19 +6221,19 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -6243,19 +6243,19 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -6287,54 +6287,142 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:03 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:09 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:49 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:09 PDT</t>
+          <t>2026-09-29 17:20 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:18 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:18 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:18 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>dbt/models/intermediate/int_sessions_unified.sql</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -4945,19 +4945,19 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Intermediate model: one row per web or app session, with customer_id resolved (known at the time, or back-filled from the visitor's anonymous_id via int_customer_identity)</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>dbt/tests/assert_int_sessions_unified_customer_matches_resolution.sql</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -4967,19 +4967,19 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>dbt test: customer_id is null exactly when a session is anonymous</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>dbt/tests/assert_int_sessions_unified_counts_match_sources.sql</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -4989,19 +4989,19 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>dbt test: unified session count equals web + app session counts</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/tests/assert_int_sessions_unified_no_negative_duration.sql</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>dbt test: no session ends before it starts</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 17:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -5033,19 +5033,19 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -5099,19 +5099,19 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,19 +5143,19 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,19 +5165,19 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,19 +5275,19 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,19 +5297,19 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,19 +5363,19 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,19 +5385,19 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,19 +5407,19 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,19 +5473,19 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,19 +5495,19 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,19 +5561,19 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,19 +5583,19 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5649,19 +5649,19 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5737,107 +5737,107 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -5881,95 +5881,95 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -5979,19 +5979,19 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -6001,19 +6001,19 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -6035,17 +6035,17 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -6057,17 +6057,17 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -6079,17 +6079,17 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -6101,17 +6101,17 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6123,117 +6123,117 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -6243,19 +6243,19 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -6287,19 +6287,19 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -6309,19 +6309,19 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -6331,19 +6331,19 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -6353,19 +6353,19 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -6375,54 +6375,142 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:09 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:20 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:49 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:20 PDT</t>
+          <t>2026-09-29 17:25 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:23 PDT</t>
+          <t>2026-09-29 18:17 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:23 PDT</t>
+          <t>2026-09-29 18:17 PDT</t>
         </is>
       </c>
     </row>
@@ -5023,29 +5023,29 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>OVERNIGHT_PLAN.md</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Runbook for the unattended overnight run: queue, rules, stop rules, morning list format</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 18:17 PDT</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -5055,19 +5055,19 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,19 +5187,19 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,19 +5297,19 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,19 +5407,19 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,19 +5517,19 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -5627,19 +5627,19 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5649,19 +5649,19 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5715,19 +5715,19 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5737,19 +5737,19 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5759,19 +5759,19 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -5825,41 +5825,41 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -5969,29 +5969,29 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -6001,19 +6001,19 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -6023,19 +6023,19 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -6211,51 +6211,51 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -6353,19 +6353,19 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -6375,19 +6375,19 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -6463,54 +6463,76 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:20 PDT</t>
+          <t>2026-09-29 16:08 PDT</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:25 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:49 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:25 PDT</t>
+          <t>2026-09-29 18:25 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:17 PDT</t>
+          <t>2026-09-29 18:55 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:17 PDT</t>
+          <t>2026-09-29 18:55 PDT</t>
         </is>
       </c>
     </row>
@@ -5038,80 +5038,80 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:17 PDT</t>
+          <t>2026-09-29 18:25 PDT</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
+          <t>OVERNIGHT_PLAN_CLAUDE_CODE.md</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
+          <t>Overnight runbook variant for Claude Code: dbt builds and branch pushes allowed</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 18:55 PDT</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
+          <t>CLAUDE.md</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
+          <t>Claude Code project instructions: standing rules, dbt/git/MotherDuck limits, start-of-session reading</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 18:55 PDT</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
+          <t>.claude/settings.json</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
+          <t>Claude Code permissions: allow dbt/git commit/push overnight branch; deny push to master, force push, rm</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-29 18:55 PDT</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
+          <t>dbt/models/marts/mart_storefront_revenue_monthly.sql</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -5121,19 +5121,19 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
+          <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:26 PDT</t>
+          <t>2026-09-28 14:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_addresses.sql</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__devices.sql</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__identity_map.sql</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__segments.sql</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -5209,19 +5209,19 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__customer_segment_membership.sql</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__subscription_events.sql</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -5253,19 +5253,19 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
+          <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 10:26 PDT</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -5275,19 +5275,19 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
+          <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:58 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_sessions.sql</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__web_events.sql</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_sessions.sql</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__app_events.sql</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -5363,19 +5363,19 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
+          <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 12:58 PDT</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -5385,19 +5385,19 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
+          <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:59 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_campaigns.sql</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_campaigns.sql</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_email_events.sql</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -5451,19 +5451,19 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
+          <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__braze_push_events.sql</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -5473,19 +5473,19 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
+          <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 12:59 PDT</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -5495,19 +5495,19 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
+          <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:02 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_campaigns.sql</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
+          <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ads.sql</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -5539,19 +5539,19 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_insights_daily.sql</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -5561,19 +5561,19 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__meta_ad_actions_daily.sql</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -5583,19 +5583,19 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
+          <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 13:02 PDT</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -5605,19 +5605,19 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
+          <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:13 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_campaigns.sql</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_ad_groups.sql</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -5649,19 +5649,19 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_performance_daily.sql</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -5671,19 +5671,19 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
+          <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__google_search_keyword_performance_daily.sql</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -5693,19 +5693,19 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
+          <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 13:13 PDT</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -5715,19 +5715,19 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
+          <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:14 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_campaigns.sql</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -5737,19 +5737,19 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_ad_groups.sql</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -5759,19 +5759,19 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
+          <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__youtube_performance_daily.sql</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
+          <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 13:14 PDT</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
+          <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:19 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -5825,19 +5825,19 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>generator/params.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_line_items.sql</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -5847,85 +5847,85 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
+          <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:23 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>data/meta_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_performance_daily.sql</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:19 PDT</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>data/google_search_campaigns.csv</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
+          <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>data/youtube_campaigns.csv</t>
+          <t>generator/params.py</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:24 PDT</t>
+          <t>2026-09-29 13:23 PDT</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>data/dv360_insertion_orders.csv</t>
+          <t>data/meta_campaigns.csv</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>data/snap_campaigns.csv</t>
+          <t>data/google_search_campaigns.csv</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_campaigns.csv</t>
+          <t>data/youtube_campaigns.csv</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
+          <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -5991,73 +5991,73 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/dv360_insertion_orders.csv</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
+          <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
+          <t>data/snap_campaigns.csv</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
+          <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:27 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>generator/paid_media_common.py</t>
+          <t>data/tiktok_campaigns.csv</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
+          <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:24 PDT</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>generator/build_meta_ad_insights_daily.py</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -6067,19 +6067,19 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>generator/build_snap_stats_daily.py</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__dv360_insertion_orders.sql</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -6089,19 +6089,19 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:29 PDT</t>
+          <t>2026-09-29 13:27 PDT</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>generator/build_tiktok_reports_daily.py</t>
+          <t>generator/paid_media_common.py</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
+          <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>generator/build_youtube_performance_daily.py</t>
+          <t>generator/build_meta_ad_insights_daily.py</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -6145,17 +6145,17 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_insights_daily.csv</t>
+          <t>generator/build_snap_stats_daily.py</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>data/meta_ad_actions_daily.csv</t>
+          <t>generator/build_tiktok_reports_daily.py</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -6189,17 +6189,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>data/snap_stats_daily.csv</t>
+          <t>generator/build_youtube_performance_daily.py</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Shipped table</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
+          <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>data/tiktok_reports_daily.csv</t>
+          <t>data/meta_ad_insights_daily.csv</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
+          <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -6233,95 +6233,95 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>docs/cross_dataset_alignment_audit.md</t>
+          <t>data/meta_ad_actions_daily.csv</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Docs</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
+          <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:54 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>generator/audit_cross_dataset_alignment.py</t>
+          <t>data/snap_stats_daily.csv</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
+          <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:30 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
+          <t>data/tiktok_reports_daily.csv</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Shipped table</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
+          <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:29 PDT</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
+          <t>docs/cross_dataset_alignment_audit.md</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
+          <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:54 PDT</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
+          <t>generator/audit_cross_dataset_alignment.py</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -6331,19 +6331,19 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
+          <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:53 PDT</t>
+          <t>2026-09-29 13:30 PDT</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_campaigns.sql</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
+          <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ad_squads.sql</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -6375,19 +6375,19 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_ads.sql</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -6397,19 +6397,19 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
+          <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__snap_stats_daily.sql</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -6419,19 +6419,19 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
+          <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 15:53 PDT</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
+          <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -6441,19 +6441,19 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
+          <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:57 PDT</t>
+          <t>2026-09-29 16:49 PDT</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_campaigns.sql</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+          <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_adgroups.sql</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -6485,54 +6485,120 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:08 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>HANDOFF.md</t>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_ads.sql</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+          <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:25 PDT</t>
+          <t>2026-09-29 15:57 PDT</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__tiktok_reports_daily.sql</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:57 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/staging/kinetic/stg_kinetic__product_variants.sql</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>HANDOFF.md</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 17:25 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
           <t>dbt/models/staging/kinetic/_kinetic__staging.yml</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
         <is>
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:49 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:25 PDT</t>
+          <t>2026-09-29 22:03 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:55 PDT</t>
+          <t>2026-09-29 22:03 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:55 PDT</t>
+          <t>2026-09-29 22:04 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:23 PDT</t>
+          <t>2026-09-29 22:03 PDT</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:25 PDT</t>
+          <t>2026-09-29 22:03 PDT</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:55 PDT</t>
+          <t>2026-09-29 19:22 PDT</t>
         </is>
       </c>
     </row>
@@ -6601,6 +6601,94 @@
       <c r="D280" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 16:49 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/int_messaging_events.sql</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Intermediate model: one row per Braze email or push event in one shape, customer resolved via Braze id or email match (written and hand-verified; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:03 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_int_messaging_events_counts_match_sources.sql</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: unified event count equals email + push event counts</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:03 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_int_messaging_events_customer_matches_resolution.sql</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: customer_id is null exactly when a messaging event is unresolved</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:03 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>MORNING_LIST.md</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Overnight run report: commands to run first, assumed decisions, done/blocked units, proposed playbook wording</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:02 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D284"/>
+  <dimension ref="A1:D287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:03 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:03 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:04 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:03 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -6689,6 +6689,72 @@
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:02 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/int_paid_media_daily.sql</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Intermediate model: one row per ad platform per day, spend/impressions/clicks/conversions in USD (written and hand-verified; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_int_paid_media_daily_spend_matches_sources.sql</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: platform-day spend total equals the six source spend totals</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_int_paid_media_daily_no_missing_days.sql</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: no missing days per platform</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:02 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:18 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:53 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:02 PDT</t>
+          <t>2026-09-29 22:05 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:02 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:03 PDT</t>
+          <t>2026-09-29 22:06 PDT</t>
         </is>
       </c>
     </row>
@@ -6755,6 +6755,94 @@
       <c r="D287" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:05 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/intermediate/int_subscription_data_through.sql</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Intermediate model: one row, the last date the subscription/invoice data covers (shared by MRR and subscriber-movement marts) (written; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:07 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/mart_subscriber_movement_monthly.sql</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4 mart (CEO): new/returning/churned/net-new/active paying subscribers by month (written and hand-validated; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:07 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_mart_subscriber_movement_monthly_identity.sql</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: end-of-month active = previous + new - churned</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:07 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_mart_subscriber_movement_monthly_totals_match_source.sql</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: total new and churned match the paid-periods source</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D291"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:05 PDT</t>
+          <t>2026-09-29 22:07 PDT</t>
         </is>
       </c>
     </row>
@@ -6843,6 +6843,94 @@
       <c r="D291" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:07 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/mart_paid_media_monthly.sql</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>dbt/models/marts/mart_acquisition_efficiency_monthly.sql</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_mart_paid_media_monthly_spend_matches_daily.sql</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: monthly paid media spend equals daily total</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>dbt/tests/assert_mart_acquisition_efficiency_monthly_spend_matches_daily.sql</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>dbt test: CAC mart spend equals total paid media spend</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:08 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:08 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:08 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:43 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:49 PDT</t>
+          <t>2026-09-29 22:11 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:07 PDT</t>
+          <t>2026-09-29 22:08 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D295"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:12 PDT</t>
+          <t>2026-09-29 22:13 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:08 PDT</t>
+          <t>2026-09-29 22:13 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:12 PDT</t>
+          <t>2026-09-29 22:13 PDT</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:06 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:08 PDT</t>
+          <t>2026-09-29 22:12 PDT</t>
         </is>
       </c>
     </row>
@@ -6931,6 +6931,50 @@
       <c r="D295" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:08 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>dbt/drafts/semantic_layer_DRAFT.yml</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>DRAFT Phase 6 semantic layer (MetricFlow semantic models + metrics) for the marts built so far; unvalidated, outside model-paths</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>docs/semantic_layer_validation_DRAFT.md</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>DRAFT Phase 6 validation set: mf query commands with expected values from hand SQL (not yet run)</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:13 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D297"/>
+  <dimension ref="A1:D298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:13 PDT</t>
+          <t>2026-09-29 22:14 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:13 PDT</t>
+          <t>2026-09-29 22:14 PDT</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 17:25 PDT</t>
+          <t>2026-09-29 22:14 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:12 PDT</t>
+          <t>2026-09-29 22:14 PDT</t>
         </is>
       </c>
     </row>
@@ -6973,6 +6973,28 @@
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 22:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>docs/kinetic_skill_DRAFT.md</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules (not reviewed by data owner)</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:13 PDT</t>
         </is>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D298"/>
+  <dimension ref="A1:D299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:13 PDT</t>
+          <t>2026-09-30 08:17 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:14 PDT</t>
+          <t>2026-09-30 08:17 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:14 PDT</t>
+          <t>2026-09-30 08:17 PDT</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:14 PDT</t>
+          <t>2026-09-30 08:10 PDT</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:14 PDT</t>
+          <t>2026-09-30 06:53 PDT</t>
         </is>
       </c>
     </row>
@@ -6997,6 +6997,28 @@
       <c r="D298" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 22:13 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>docs/metrics_glossary.md</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:17 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D299"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:17 PDT</t>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:17 PDT</t>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:17 PDT</t>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 18:55 PDT</t>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 19:22 PDT</t>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:10 PDT</t>
+          <t>2026-09-30 08:29 PDT</t>
         </is>
       </c>
     </row>
@@ -7019,6 +7019,28 @@
       <c r="D299" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 08:17 PDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>scripts/rebuild_docs_branch.sh</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:34 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="File Manifest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="File Manifest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,11 +482,7 @@
           <t>Project overview and folder structure guide</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:47 PDT</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -504,11 +500,7 @@
           <t>Plain-English log of every decision and build step</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:34 PDT</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,11 +518,7 @@
           <t>Kinetic business model: subscriptions, courses, merch, seasonality</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -548,11 +536,7 @@
           <t>Full 47-table schema reference across all domains</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -570,11 +554,7 @@
           <t>Build sequence, validation approach, canonical metrics, locked conventions</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,11 +572,7 @@
           <t>Phase 0 Step 1: global constants (scale, dates, pricing, rates)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:23 PDT</t>
-        </is>
-      </c>
+      <c r="D7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -614,11 +590,7 @@
           <t>Phase 0 Steps 2-3: builds seasonality calendar + channel mix schedule</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,11 +608,7 @@
           <t>Builds/refreshes this file manifest spreadsheet</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:34 PDT</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -658,11 +626,7 @@
           <t>Weekly demand multiplier driving signups/spend/traffic</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -680,11 +644,7 @@
           <t>Acquisition channel share over time (Meta/Google/YouTube/DV360/Snap/TikTok/organic)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -702,11 +662,7 @@
           <t>Visual sanity-check of the seasonality calendar</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -724,11 +680,7 @@
           <t>Excludes Python __pycache__ from git/sync</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:43 PDT</t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -748,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:34 PDT</t>
+          <t>2026-09-30 08:55 PDT</t>
         </is>
       </c>
     </row>
@@ -768,11 +720,7 @@
           <t>Shared weighted date/channel sampling helpers</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -790,11 +738,7 @@
           <t>Phase 0 Step 4: builds the ~2,000-person anonymous ghost population (anon_id now hash-derived, not uuid4 -- reproducibility fix)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -812,11 +756,7 @@
           <t>Phase 0 Steps 5-6: per-customer master timeline + attribution ground truth (fixed: course_merch_only orders now reconciled against the eventual subscription window; pre_signup_anon_id now hash-derived, not uuid4)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,11 +774,7 @@
           <t>Anonymous visitors who never become tracked customers; source of guest merch orders</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -856,11 +792,7 @@
           <t>Full nested ground-truth simulation for all 100 customers (signup, trial, subscriptions, orders, churn)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -878,11 +810,7 @@
           <t>Flattened, spreadsheet-readable summary of the customer timeline</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -900,11 +828,7 @@
           <t>True acquisition/reactivation channel per customer, kept separate from intentionally messy shipped UTM data</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -922,11 +846,7 @@
           <t>Builds the funnel + segment breakdown charts for the simulation analysis</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -944,11 +864,7 @@
           <t>Customer funnel: total -&gt; trial started -&gt; converted -&gt; active today</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -966,11 +882,7 @@
           <t>Part-to-whole breakdown of all customers' current status</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -988,11 +900,7 @@
           <t>Summary analysis of the recalibrated Phase 0 simulation results</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1010,11 +918,7 @@
           <t>Phase 1: builds the products table (~12-item course/merch catalog)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1032,11 +936,7 @@
           <t>Phase 1: 5-layer validation for products (structural/referential/temporal/business-rule/distributional)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,11 +954,7 @@
           <t>Phase 1: products table (course + merch catalog)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1076,11 +972,7 @@
           <t>Phase 1: builds product_variants (sizes for apparel, single variant elsewhere)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1098,11 +990,7 @@
           <t>Phase 1: 5-layer validation for product_variants, including FK to products</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1120,11 +1008,7 @@
           <t>Phase 1: product_variants table (21 variants across 12 products)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1142,11 +1026,7 @@
           <t>Phase 1: builds subscription_plans (Basic/Plus x monthly/annual)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1164,11 +1044,7 @@
           <t>Phase 1: 5-layer validation for subscription_plans</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1186,11 +1062,7 @@
           <t>Phase 1: subscription_plans table (4 plans)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1208,11 +1080,7 @@
           <t>Phase 1: builds customers table from the master timeline; defines customer_id mapping</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1230,11 +1098,7 @@
           <t>Phase 1: 5-layer validation for customers, incl. 1:1 reconciliation vs. the timeline</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1252,11 +1116,7 @@
           <t>Phase 1: customers table (860 rows, one per simulated customer)</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1274,11 +1134,7 @@
           <t>Phase 1: builds customer_addresses (billing/shipping, obviously-fake streets)</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1296,11 +1152,7 @@
           <t>Phase 1: 5-layer validation for customer_addresses</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1318,11 +1170,7 @@
           <t>Phase 1: customer_addresses table (1,431 rows)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1340,11 +1188,7 @@
           <t>Phase 1: builds devices (customer + anonymous-ghost devices; 2nd-device anon_id now hash-derived, not uuid4)</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1362,11 +1206,7 @@
           <t>Phase 1: 5-layer validation for devices</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1384,11 +1224,7 @@
           <t>Phase 1: devices table (18,042 rows: known-customer + ghost devices)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1406,11 +1242,7 @@
           <t>Phase 1: builds identity_map (anonymous_id -&gt; customer_id resolution events)</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1428,11 +1260,7 @@
           <t>Phase 1: 5-layer validation for identity_map</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1450,11 +1278,7 @@
           <t>Phase 1: identity_map table (992 rows)</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1472,11 +1296,7 @@
           <t>Phase 1: builds segments (27 definitions: 9 customer-grain, 18 anonymous -- 3 audience concepts x 6 ad platforms)</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1494,11 +1314,7 @@
           <t>Phase 1: 5-layer validation for segments</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1516,11 +1332,7 @@
           <t>Phase 1: segments table (27 rows) -- completes Phase 1 (all 8 tables)</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1538,11 +1350,7 @@
           <t>Phase 2: builds subscriptions (Stripe-shaped subscription objects; assigns billing_interval + next-renewal date, resolving the long-flagged Phase 2 gap)</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1560,11 +1368,7 @@
           <t>Phase 2: 5-layer validation for subscriptions</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1582,11 +1386,7 @@
           <t>Phase 2: subscriptions table (576 rows: one Stripe-shaped subscription object per trial-or-interval)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1604,11 +1404,7 @@
           <t>Phase 2: builds subscription_events (event log behind every subscription: trial_started/converted/expired, renewed, upgraded/downgraded, payment_failed, canceled, resumed)</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1626,11 +1422,7 @@
           <t>Phase 2: 5-layer validation for subscription_events</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1648,11 +1440,7 @@
           <t>Phase 2: subscription_events table (2,423 rows, incl. ~3% deliberate duplicate webhook-style rows)</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1670,11 +1458,7 @@
           <t>Phase 2: builds invoices (one per initial charge + renewal, plus uncollectible/open for failed payments) -- completes Phase 2 (all 3 tables)</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1692,11 +1476,7 @@
           <t>Phase 2: 5-layer validation for invoices</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1714,11 +1494,7 @@
           <t>Phase 2: invoices table (1,229 rows) -- completes Phase 2</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1736,11 +1512,7 @@
           <t>Phase 3: builds discount_codes (hand-curated list: evergreen + seasonal promo codes) -- built first in Phase 3 since orders needs it</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1758,11 +1530,7 @@
           <t>Phase 3: 5-layer validation for discount_codes</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1780,11 +1548,7 @@
           <t>Phase 3: discount_codes table (7 rows)</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1802,11 +1566,7 @@
           <t>Phase 3: builds orders (customer course/merch + guest merch), cross-validated against subscriptions.csv</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1824,11 +1584,7 @@
           <t>Phase 3: 5-layer validation for orders, incl. the no-course-during-subscription cross-check</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1846,11 +1602,7 @@
           <t>Phase 3: orders table (3,650 rows: 1,061 course + 1,332 customer-merch + 1,257 guest-merch)</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1868,11 +1620,7 @@
           <t>Phase 3: builds order_line_items (one row per order -- resolves each order's price tier down to a specific product + variant)</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1890,11 +1638,7 @@
           <t>Phase 3: 5-layer validation for order_line_items</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1912,11 +1656,7 @@
           <t>Phase 3: order_line_items table (3,650 rows, one per order)</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1934,11 +1674,7 @@
           <t>Phase 3: builds payments (one Stripe-shaped Charge attempt per row; models realistic declined-then-retried charge attempts)</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1956,11 +1692,7 @@
           <t>Phase 3: 5-layer validation for payments</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1978,11 +1710,7 @@
           <t>Phase 3: payments table (3,964 rows: 3,650 succeeded + 314 failed retry attempts)</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2000,11 +1728,7 @@
           <t>Phase 3: builds refunds (against a small share of orders' succeeded payments) -- completes Phase 3 (all 5 tables)</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2022,11 +1746,7 @@
           <t>Phase 3: 5-layer validation for refunds</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2044,11 +1764,7 @@
           <t>Phase 3: refunds table (159 rows, 4.4% of orders) -- completes Phase 3</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2066,11 +1782,7 @@
           <t>Phase 4: builds customer_segment_membership (effective-dated, derived entirely from subscriptions/orders/invoices -- seg_009 skipped, needs Phase 5) -- completes Phase 4</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2088,11 +1800,7 @@
           <t>Phase 4: 5-layer validation for customer_segment_membership</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2110,11 +1818,7 @@
           <t>Phase 4: customer_segment_membership table (2,234 rows across 8 of 9 customer-grain segments) -- completes Phase 4</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2132,11 +1836,7 @@
           <t>Phase 5: builds web_sessions (marketing-site browsing; known customers + anonymous ghosts, engagement_tier-driven volume)</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2154,11 +1854,7 @@
           <t>Phase 5: 5-layer validation for web_sessions</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2176,11 +1872,7 @@
           <t>Phase 5: web_sessions table (30,285 rows: 6,476 identity-resolved + 23,809 anonymous)</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2198,11 +1890,7 @@
           <t>Phase 5: builds web_events (page_view/product_view/add_to_cart/begin_checkout/purchase/search; every order gets exactly one purchase event)</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2220,11 +1908,7 @@
           <t>Phase 5: 5-layer validation for web_events</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2242,11 +1926,7 @@
           <t>Phase 5: web_events table (117,706 rows)</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2264,11 +1944,7 @@
           <t>Phase 5: builds app_sessions (in-app fitness usage, driven by real subscription intervals + course orders, keyed off engagement_tier)</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2286,11 +1962,7 @@
           <t>Phase 5: 5-layer validation for app_sessions</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2308,11 +1980,7 @@
           <t>Phase 5: app_sessions table (19,610 rows across 496 customers)</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2330,11 +1998,7 @@
           <t>Phase 5: builds app_events (class_started/workout_completed/workout_abandoned/streak_achieved -- streaks derived from real consecutive session dates) -- completes Phase 5</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2352,11 +2016,7 @@
           <t>Phase 5: 5-layer validation for app_events</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2374,11 +2034,7 @@
           <t>Phase 5: app_events table (39,370 rows) -- completes Phase 5</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2396,11 +2052,7 @@
           <t>Phase 6: builds braze_email_campaigns (hand-curated: 7 triggered + 2 broadcast) -- built first, events table needs it</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2418,11 +2070,7 @@
           <t>Phase 6: 5-layer validation for braze_email_campaigns</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2440,11 +2088,7 @@
           <t>Phase 6: braze_email_campaigns table (9 rows)</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2462,11 +2106,7 @@
           <t>Phase 5: builds web_events (retroactive fix: timestamp offsets now rounded to whole seconds, fixing a latent fractional-second formatting bug across all 117,706 rows)</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2484,11 +2124,7 @@
           <t>Phase 5: web_events table (117,706 rows; retroactively rebuilt for the whole-second timestamp fix, same counts/logic)</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2506,11 +2142,7 @@
           <t>Phase 6: builds braze_email_events (Send/Open/Click/Bounce/Unsubscribe funnel, derived from real trial/payment-failure/order/cart/reactivation sources)</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2528,11 +2160,7 @@
           <t>Phase 6: 5-layer validation for braze_email_events</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2550,11 +2178,7 @@
           <t>Phase 6: braze_email_events table (26,335 rows, 18,187 sends) -- updated 2026-08-13 by the cross-dataset audit's Check 6 fix (merch_to_sub_trigger send time-of-day)</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2572,11 +2196,7 @@
           <t>Phase 6: builds braze_push_campaigns (hand-curated: 5 triggered + 2 broadcast, push-appropriate subset) -- built before events table needs it</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2594,11 +2214,7 @@
           <t>Phase 6: 5-layer validation for braze_push_campaigns</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2616,11 +2232,7 @@
           <t>Phase 6: braze_push_campaigns table (7 rows)</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2638,11 +2250,7 @@
           <t>Phase 6: builds braze_push_events (Send/Open/Click/Bounce/Unsubscribe funnel, gated on push_opt_in as a hard delivery precondition) -- completes Phase 6 (all 4 tables)</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2660,11 +2268,7 @@
           <t>Phase 6: 5-layer validation for braze_push_events</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2682,11 +2286,7 @@
           <t>Phase 6: braze_push_events table (9,897 rows, 7,851 sends) -- completes Phase 6 (25 of 47 tables shipped; Phase 7 paid media remains)</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2704,11 +2304,7 @@
           <t>Phase 7: shared helpers used by all 6 platforms' daily performance tables -- maps any date to the seasonality calendar/channel-mix week and draws each day's per-channel spend baseline</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2726,11 +2322,7 @@
           <t>Phase 7 (Meta 1/4): builds meta_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns timed near BFCM)</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2748,11 +2340,7 @@
           <t>Phase 7: 5-layer validation for meta_campaigns</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2770,11 +2358,7 @@
           <t>Phase 7 (Meta 1/4): meta_campaigns table (7 rows)</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2792,11 +2376,7 @@
           <t>Phase 7 (Meta 2/4): builds meta_ads (functions as the ad-set-level entity -- targeting_segment_id for retargeting/lookalike only)</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2814,11 +2394,7 @@
           <t>Phase 7: 5-layer validation for meta_ads</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2836,11 +2412,7 @@
           <t>Phase 7 (Meta 2/4): meta_ads table (10 rows)</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2858,11 +2430,7 @@
           <t>Phase 7 (Meta 3/4): builds meta_ad_insights_daily (spend/impressions/clicks driven by the shared seasonality calendar + channel-mix schedule)</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2880,11 +2448,7 @@
           <t>Phase 7: 5-layer validation for meta_ad_insights_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2902,11 +2466,7 @@
           <t>Phase 7 (Meta 3/4): meta_ad_insights_daily table (7,396 rows)</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2924,11 +2484,7 @@
           <t>Phase 7 (Meta 4/4): builds meta_ad_actions_daily (normalized actions array, derived directly from meta_ad_insights_daily.csv's own clicks) -- completes Meta (1 of 6 platforms)</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2946,11 +2502,7 @@
           <t>Phase 7: 5-layer validation for meta_ad_actions_daily</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2968,11 +2520,7 @@
           <t>Phase 7 (Meta 4/4): meta_ad_actions_daily table (35,504 rows) -- completes Meta</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2990,11 +2538,7 @@
           <t>Phase 7 (Google Search 1/4): builds google_search_campaigns (5 evergreen objective campaigns, incl. an always-on brand-term defense campaign)</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3012,11 +2556,7 @@
           <t>Phase 7: 5-layer validation for google_search_campaigns</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3034,11 +2574,7 @@
           <t>Phase 7 (Google Search 1/4): google_search_campaigns table (5 rows)</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3056,11 +2592,7 @@
           <t>Phase 7 (Google Search 2/4): builds google_search_ad_groups (targeting_segment_id for RLSA retargeting/similar-audience lookalike only)</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3078,11 +2610,7 @@
           <t>Phase 7: 5-layer validation for google_search_ad_groups</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3100,11 +2628,7 @@
           <t>Phase 7 (Google Search 2/4): google_search_ad_groups table (8 rows)</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3122,11 +2646,7 @@
           <t>Phase 7 (Google Search 4/4 by build order): builds google_search_keyword_performance_daily -- the granular ground truth google_search_performance_daily aggregates from</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3144,11 +2664,7 @@
           <t>Phase 7: 5-layer validation for google_search_keyword_performance_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3166,11 +2682,7 @@
           <t>Phase 7 (Google Search 4/4 by build order): google_search_keyword_performance_daily table (19,932 rows)</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3188,11 +2700,7 @@
           <t>Phase 7 (Google Search 3/4 by schema order): builds google_search_performance_daily, aggregated exactly from keyword_performance_daily.csv up to ad_group/day grain -- completes Google Search (2 of 6 platforms)</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3210,11 +2718,7 @@
           <t>Phase 7: 5-layer validation for google_search_performance_daily, incl. exact-sum reconciliation against keyword_performance_daily.csv</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3232,11 +2736,7 @@
           <t>Phase 7 (Google Search 3/4 by schema order): google_search_performance_daily table (8,751 rows) -- completes Google Search</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3254,11 +2754,7 @@
           <t>Phase 7 (YouTube 1/3): builds youtube_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns, mirroring Meta's structure since YouTube Brand Lift is a real flighted measurement product)</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3276,11 +2772,7 @@
           <t>Phase 7: 5-layer validation for youtube_campaigns</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3298,11 +2790,7 @@
           <t>Phase 7 (YouTube 1/3): youtube_campaigns table (7 rows)</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3320,11 +2808,7 @@
           <t>Phase 7 (YouTube 2/3): builds youtube_ad_groups (targeting_segment_id for retargeting/lookalike only)</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3342,11 +2826,7 @@
           <t>Phase 7: 5-layer validation for youtube_ad_groups</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3364,11 +2844,7 @@
           <t>Phase 7 (YouTube 2/3): youtube_ad_groups table (9 rows)</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3386,11 +2862,7 @@
           <t>Phase 7 (YouTube 3/3): builds youtube_performance_daily (video_views/video_view_rate/average_cpv, spend-driven by the shared seasonality calendar + channel-mix schedule) -- completes YouTube (3 of 6 platforms)</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3408,11 +2880,7 @@
           <t>Phase 7: 5-layer validation for youtube_performance_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3430,11 +2898,7 @@
           <t>Phase 7 (YouTube 3/3): youtube_performance_daily table (6,394 rows) -- completes YouTube</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3452,11 +2916,7 @@
           <t>Phase 7 (DV360 1/3): builds dv360_insertion_orders (5 evergreen objective IOs, incl. a VIEWABLE_CPM awareness IO)</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3474,11 +2934,7 @@
           <t>Phase 7: 5-layer validation for dv360_insertion_orders</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3496,11 +2952,7 @@
           <t>Phase 7 (DV360 1/3): dv360_insertion_orders table (5 rows)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3518,11 +2970,7 @@
           <t>Phase 7 (DV360 2/3): builds dv360_line_items (targeting_segment_id for retargeting/lookalike only; brand_lift IO's line item is VIDEO type)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3540,11 +2988,7 @@
           <t>Phase 7: 5-layer validation for dv360_line_items</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3562,11 +3006,7 @@
           <t>Phase 7 (DV360 2/3): dv360_line_items table (6 rows)</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3584,11 +3024,7 @@
           <t>Phase 7 (DV360 3/3): builds dv360_performance_daily -- fragments each line_item/day into several (exchange, environment) rows, DV360's genuinely different real-time-bidding schema shape -- completes DV360 (4 of 6 platforms)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3606,11 +3042,7 @@
           <t>Phase 7: 5-layer validation for dv360_performance_daily, incl. weekly-spend-vs-web_sessions correlation check and CONNECTED_TV-only-on-video-line-item check</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3628,11 +3060,7 @@
           <t>Phase 7 (DV360 3/3): dv360_performance_daily table (25,776 rows) -- completes DV360</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3650,11 +3078,7 @@
           <t>Phase 7 (Snap 1/4): builds snap_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns, flight budgets calibrated to avoid YouTube's earlier scale bug)</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3672,11 +3096,7 @@
           <t>Phase 7: 5-layer validation for snap_campaigns</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3694,11 +3114,7 @@
           <t>Phase 7 (Snap 1/4): snap_campaigns table (7 rows)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3716,11 +3132,7 @@
           <t>Phase 7 (Snap 2/4): builds snap_ad_squads (Snap's own real ad-set-level targeting entity, unlike Meta -- targeting_segment_id for retargeting/lookalike only)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3738,11 +3150,7 @@
           <t>Phase 7: 5-layer validation for snap_ad_squads</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3760,11 +3168,7 @@
           <t>Phase 7 (Snap 2/4): snap_ad_squads table (8 rows)</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -3782,11 +3186,7 @@
           <t>Phase 7 (Snap 3/4): builds snap_ads (creative-level entity, no targeting -- that lives on the ad squad)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -3804,11 +3204,7 @@
           <t>Phase 7: 5-layer validation for snap_ads</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3826,11 +3222,7 @@
           <t>Phase 7 (Snap 3/4): snap_ads table (10 rows)</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3848,11 +3240,7 @@
           <t>Phase 7 (Snap 4/4): builds snap_stats_daily (spend in Snap's own micro-currency unit, swipes as the click-equivalent) -- completes Snap (5 of 6 platforms)</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3870,11 +3258,7 @@
           <t>Phase 7: 5-layer validation for snap_stats_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3892,11 +3276,7 @@
           <t>Phase 7 (Snap 4/4): snap_stats_daily table (7,407 rows) -- completes Snap</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3914,11 +3294,7 @@
           <t>Phase 7 (TikTok 1/4): builds tiktok_campaigns (4 evergreen objective campaigns + 3 flighted brand_lift campaigns)</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3936,11 +3312,7 @@
           <t>Phase 7: 5-layer validation for tiktok_campaigns</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -3958,11 +3330,7 @@
           <t>Phase 7 (TikTok 1/4): tiktok_campaigns table (7 rows)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3980,11 +3348,7 @@
           <t>Phase 7 (TikTok 2/4): builds tiktok_adgroups (TikTok's own real ad-set-level targeting entity -- targeting_segment_id for retargeting/lookalike only)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4002,11 +3366,7 @@
           <t>Phase 7: 5-layer validation for tiktok_adgroups</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4024,11 +3384,7 @@
           <t>Phase 7 (TikTok 2/4): tiktok_adgroups table (8 rows)</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4046,11 +3402,7 @@
           <t>Phase 7 (TikTok 3/4): builds tiktok_ads (creative-level entity, no targeting -- that lives on the ad group)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4068,11 +3420,7 @@
           <t>Phase 7: 5-layer validation for tiktok_ads</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4090,11 +3438,7 @@
           <t>Phase 7 (TikTok 3/4): tiktok_ads table (10 rows)</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4112,11 +3456,7 @@
           <t>Phase 7 (TikTok 4/4): builds tiktok_reports_daily (spend/impressions/video_views, TikTok's always-video ad format) -- completes TikTok (6 of 6 platforms) AND all 47 tables</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4134,11 +3474,7 @@
           <t>Phase 7: 5-layer validation for tiktok_reports_daily, incl. weekly-spend-vs-web_sessions correlation check</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4156,11 +3492,7 @@
           <t>Phase 7 (TikTok 4/4): tiktok_reports_daily table (7,416 rows) -- completes TikTok, Phase 7, and the full 47-table dataset</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4178,11 +3510,7 @@
           <t>Post-completion cross-dataset alignment audit -- NOT a shipped-table script. 7 checks: aggregate spend vs. demand, channel mix vs. schedule, calendar-event alignment, long-run growth trend, renewal/lag structure, day-of-week/hour-of-day, timezone/precision sweep. Found and fixed a real bug (Check 6 -- merch_to_sub_trigger Braze sends all landing at exactly midnight); Checks 3 and 5 surfaced genuine, documented (non-bug) characteristics.</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:30 PDT</t>
-        </is>
-      </c>
+      <c r="D170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -4200,11 +3528,7 @@
           <t>Write-up of the 7-check cross-dataset alignment audit's results, including the merch_to_sub_trigger bug fix and the two documented (non-bug) findings from Checks 3 and 5</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:54 PDT</t>
-        </is>
-      </c>
+      <c r="D171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4222,11 +3546,7 @@
           <t>Post-dataset-completion tooling -- loads all 47 CSVs into a free MotherDuck (hosted DuckDB) database, one table per CSV, with a row-count verification per table. Run on the user's own machine, not inside the Cowork cloud sandbox (MotherDuck needs outbound internet the sandbox doesn't have). Reads its motherduck_token from either a shell env var or an optional warehouse/.env file (gitignored -- NOT tracked or synced by this manifest, since it holds a live credential). Confirmed working end-to-end against the user's own MotherDuck account (47/47 tables, exact row-count match).</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4244,11 +3564,7 @@
           <t>6 starter SQL queries against the kinetic MotherDuck database: monthly paid media spend by partner, directly attributed revenue by paid/owned channel, active subscribers by month, non-subscription revenue by month, monthly churn rate, top 5 grossing products per year. Heavily commented to explain modeling choices (e.g. the paid/owned attribution methodology split between storefront orders and subscription invoices).</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4266,11 +3582,7 @@
           <t>One-off interactive chart visualizing Query 1's actual output (pasted by the user from their own MotherDuck run): monthly paid media spend by partner, Aug 2023-Jul 2026. Multi-line chart with hover tooltip, legend isolate-toggle, dark mode, and a table view -- built per the dataviz skill (validated categorical palette, accessible contrast handling).</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4288,11 +3600,7 @@
           <t>Source for the 'Kinetic -- Marketing &amp; Revenue Overview' MotherDuck Dive -- a live, hosted interactive dashboard (React/Recharts), now organized as 5 tabs. Overview tab: the original 6 starter queries + KPI row. CEO tab: revenue growth/net-new-vs-churned subscribers/CAC payback, revenue mix (subscription vs. course vs. merch). CMO tab: acquisition funnel by channel (sessions -&gt; trial starts -&gt; conversions), retention/app engagement by acquisition channel. CFO tab: CAC and LTV:CAC by acquisition cohort, discount code cost + failed-payment recovery rate + a documented net-margin proxy (no COGS data exists for a true gross margin). Performance Marketing tab: campaign-level spend and platform-self-reported efficiency across all 38 real campaigns (sorted worst-CAC-first), CTR/CVR by platform and ad format. Each new section documents its modeling limits explicitly (e.g. platform-reported vs. site-attributed conversions have no shared join key in this dataset). Re-runs live SQL against the kinetic database on every open. Saved to MotherDuck via the MCP tools; this file is the local source-of-truth copy for sync/history. Live at https://app.motherduck.com/dives/kinetic-marketing-revenue-overview-58909b4e-d301-4794-bb59-ce46f9dc73a6 (dive_id 58909b4e-d301-4794-bb59-ce46f9dc73a6, version 2).</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:09 PDT</t>
-        </is>
-      </c>
+      <c r="D175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4310,11 +3618,7 @@
           <t>Updated 2026-09-28: real project status (47/47 tables built+validated, live in MotherDuck) + direct link to the live Dive dashboard, replacing the stale 'planning complete, next step Phase 0' placeholder text</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:47 PDT</t>
-        </is>
-      </c>
+      <c r="D176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4332,11 +3636,7 @@
           <t>Updated 2026-09-28: closed the one open item (brand_lift/holiday-discount-code asymmetry across the 3 Novembers) -- reviewed and confirmed intentional, no data changed</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:54 PDT</t>
-        </is>
-      </c>
+      <c r="D177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4354,11 +3654,7 @@
           <t>dbt project config for the new semantic layer -- staging views, intermediate views, mart tables</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4376,11 +3672,7 @@
           <t>dbt connection profile (MotherDuck md:kinetic, schema dbt_dev); no secrets</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:43 PDT</t>
-        </is>
-      </c>
+      <c r="D179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4398,11 +3690,7 @@
           <t>Excludes dbt's target/, dbt_packages/, logs/ from git</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -4420,11 +3708,7 @@
           <t>How to install dbt-core + dbt-duckdb and run this project locally against MotherDuck (neither of Claude's environments can reach motherduck.com directly, so dbt run/test must be executed on the user's own machine)</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:12 PDT</t>
-        </is>
-      </c>
+      <c r="D181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -4442,11 +3726,7 @@
           <t>Declares all 47 raw kinetic tables as dbt sources, so every staging model references source() rather than a hardcoded table name</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -4464,11 +3744,7 @@
           <t>Staging model: 1:1 pass-through of customers with light renaming</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -4486,11 +3762,7 @@
           <t>Staging model: 1:1 pass-through of subscription_plans</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -4508,11 +3780,7 @@
           <t>Staging model: 1:1 pass-through of subscriptions</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -4530,11 +3798,7 @@
           <t>Staging model: 1:1 pass-through of invoices</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -4552,11 +3816,7 @@
           <t>Staging model: 1:1 pass-through of products</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -4574,11 +3834,7 @@
           <t>not_null/unique/relationships tests for the Phase 1/2 staging models</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -4596,11 +3852,7 @@
           <t>Intermediate model: resolves each subscription's true paid-start date (trial-vs-paid logic), defined once so every downstream mart agrees</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:48 PDT</t>
-        </is>
-      </c>
+      <c r="D189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -4618,11 +3870,7 @@
           <t>Descriptions and tests for all intermediate models</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:12 PDT</t>
-        </is>
-      </c>
+      <c r="D190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -4640,11 +3888,7 @@
           <t>First canonical metric mart: active subscribers + MRR/ARR by month, validated against a hand-run equivalent query on the live database (2026-07: 90 active subscribers, ~$2,133 MRR)</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:07 PDT</t>
-        </is>
-      </c>
+      <c r="D191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -4662,11 +3906,7 @@
           <t>Tests for mart_mrr_monthly</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:12 PDT</t>
-        </is>
-      </c>
+      <c r="D192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -4684,11 +3924,7 @@
           <t>Updated: what's built so far now includes the Phase 3 storefront staging models + mart_storefront_revenue_monthly</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:12 PDT</t>
-        </is>
-      </c>
+      <c r="D193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -4706,11 +3942,7 @@
           <t>Staging model: 1:1 pass-through of orders, plus is_guest_order/has_discount convenience booleans</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -4728,11 +3960,7 @@
           <t>Staging model: 1:1 pass-through of order_line_items</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -4750,11 +3978,7 @@
           <t>Staging model: 1:1 pass-through of payments</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -4772,11 +3996,7 @@
           <t>Staging model: 1:1 pass-through of refunds</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -4794,11 +4014,7 @@
           <t>Staging model: 1:1 pass-through of discount_codes</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -4816,11 +4032,7 @@
           <t>Intermediate model: per-order total of succeeded refunds only (failed/pending refunds don't reduce reported revenue)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:53 PDT</t>
-        </is>
-      </c>
+      <c r="D199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -4838,11 +4050,7 @@
           <t>Intermediate model: lookup from every web anonymous_id and account email to its customer (guest emails matched by email; anonymous sessions back-filled; deleted accounts excluded)</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:39 PDT</t>
-        </is>
-      </c>
+      <c r="D200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -4860,11 +4068,7 @@
           <t>Intermediate model: one row per order with gross (pre-discount), discount, paid, succeeded-refund and net amounts, plus customer_id resolved for guest orders via email match</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:05 PDT</t>
-        </is>
-      </c>
+      <c r="D201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -4882,11 +4086,7 @@
           <t>dbt test: fails if any order's net is below zero (net is deliberately not floored)</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:18 PDT</t>
-        </is>
-      </c>
+      <c r="D202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -4904,11 +4104,7 @@
           <t>dbt test: gross - discount = paid and paid - refund = net on every order</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:18 PDT</t>
-        </is>
-      </c>
+      <c r="D203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -4926,11 +4122,7 @@
           <t>dbt test: total refunds in int_orders_net equal total succeeded refunds in int_orders_refunded</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:18 PDT</t>
-        </is>
-      </c>
+      <c r="D204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -4948,11 +4140,7 @@
           <t>Intermediate model: one row per web or app session, with customer_id resolved (known at the time, or back-filled from the visitor's anonymous_id via int_customer_identity)</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:23 PDT</t>
-        </is>
-      </c>
+      <c r="D205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -4970,11 +4158,7 @@
           <t>dbt test: customer_id is null exactly when a session is anonymous</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:23 PDT</t>
-        </is>
-      </c>
+      <c r="D206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -4992,11 +4176,7 @@
           <t>dbt test: unified session count equals web + app session counts</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:23 PDT</t>
-        </is>
-      </c>
+      <c r="D207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -5014,11 +4194,7 @@
           <t>dbt test: no session ends before it starts</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 17:23 PDT</t>
-        </is>
-      </c>
+      <c r="D208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -5036,11 +4212,7 @@
           <t>Runbook for the unattended overnight run: queue, rules, stop rules, morning list format</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:12 PDT</t>
-        </is>
-      </c>
+      <c r="D209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -5058,11 +4230,7 @@
           <t>Overnight runbook variant for Claude Code: dbt builds and branch pushes allowed</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 18:55 PDT</t>
-        </is>
-      </c>
+      <c r="D210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -5080,11 +4248,7 @@
           <t>Claude Code project instructions: standing rules, dbt/git/MotherDuck limits, start-of-session reading</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:34 PDT</t>
-        </is>
-      </c>
+      <c r="D211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -5102,11 +4266,7 @@
           <t>Claude Code permissions: allow dbt/git commit/push overnight branch; deny push to master, force push, rm</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:34 PDT</t>
-        </is>
-      </c>
+      <c r="D212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -5124,11 +4284,7 @@
           <t>Second canonical metric mart: non-subscription (course+merch) gross/net revenue, AOV, guest-checkout share, discount-usage share, refund rate by month -- validated against a hand-run equivalent query on the live database (2026-07: 246 orders, $13,843.71 gross revenue, $56.28 AOV)</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:05 PDT</t>
-        </is>
-      </c>
+      <c r="D213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -5146,11 +4302,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_addresses</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -5168,11 +4320,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of devices, plus is_anonymous_device flag (customer_id null for ~94% of devices by design)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -5190,11 +4338,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of identity_map</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -5212,11 +4356,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of segments</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -5234,11 +4374,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of customer_segment_membership, plus is_current_member flag</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -5256,11 +4392,7 @@
           <t>Phase 2 staging (Customer 360): 1:1 pass-through of subscription_events; old_plan/new_plan renamed to old_plan_id/new_plan_id</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:26 PDT</t>
-        </is>
-      </c>
+      <c r="D219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -5278,11 +4410,7 @@
           <t>Updated: tests for the 6 Customer 360 staging models (PK not_null/unique, FK relationships) -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -5300,11 +4428,7 @@
           <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_sessions, plus is_known_customer flag (customer_id null for ~79% of sessions by design)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:58 PDT</t>
-        </is>
-      </c>
+      <c r="D221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -5322,11 +4446,7 @@
           <t>Phase 2 staging (web/app engagement): 1:1 pass-through of web_events</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:58 PDT</t>
-        </is>
-      </c>
+      <c r="D222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -5344,11 +4464,7 @@
           <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_sessions</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:58 PDT</t>
-        </is>
-      </c>
+      <c r="D223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -5366,11 +4482,7 @@
           <t>Phase 2 staging (web/app engagement): 1:1 pass-through of app_events</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:58 PDT</t>
-        </is>
-      </c>
+      <c r="D224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -5388,11 +4500,7 @@
           <t>Updated: tests for the 4 web/app engagement staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -5410,11 +4518,7 @@
           <t>Phase 2 staging (email/push): 1:1 pass-through of braze_email_campaigns</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:59 PDT</t>
-        </is>
-      </c>
+      <c r="D226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -5432,11 +4536,7 @@
           <t>Phase 2 staging (email/push): 1:1 pass-through of braze_push_campaigns</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:59 PDT</t>
-        </is>
-      </c>
+      <c r="D227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -5454,11 +4554,7 @@
           <t>Phase 2 staging (email/push): braze_email_events with external_user_id renamed to customer_id and a short event_name (send/open/click/bounce/unsubscribe) alongside Braze's raw event_type</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:59 PDT</t>
-        </is>
-      </c>
+      <c r="D228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -5476,11 +4572,7 @@
           <t>Phase 2 staging (email/push): braze_push_events with external_user_id renamed to customer_id and a short event_name alongside Braze's raw event_type</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:59 PDT</t>
-        </is>
-      </c>
+      <c r="D229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -5498,11 +4590,7 @@
           <t>Updated: tests for the 4 Braze staging models, incl. accepted_values on event_name -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -5520,11 +4608,7 @@
           <t>Phase 2 staging (paid media: Meta): meta_campaigns with budgets in both raw cents and dollars (Meta API stores budgets in cents)</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:02 PDT</t>
-        </is>
-      </c>
+      <c r="D231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -5542,11 +4626,7 @@
           <t>Phase 2 staging (paid media: Meta): 1:1 pass-through of meta_ads</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:02 PDT</t>
-        </is>
-      </c>
+      <c r="D232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -5564,11 +4644,7 @@
           <t>Phase 2 staging (paid media: Meta): meta_ad_insights_daily with a combined ad_day_id key, unit-suffixed columns (spend_usd, cpm_usd, cpc_usd) and ctr renamed ctr_fraction (0.017 = 1.7%)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:02 PDT</t>
-        </is>
-      </c>
+      <c r="D233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -5586,11 +4662,7 @@
           <t>Phase 2 staging (paid media: Meta): meta_ad_actions_daily with a combined ad_day_action_id key; value renamed action_count</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:02 PDT</t>
-        </is>
-      </c>
+      <c r="D234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -5608,11 +4680,7 @@
           <t>Updated: tests for the 4 Meta staging models, incl. uniqueness of the combined daily keys -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -5630,11 +4698,7 @@
           <t>Phase 2 staging (paid media: Google Search): campaigns with the raw customer_id renamed google_ads_account_id (it's the Google Ads account number, not a Kinetic customer), daily budget in micros and dollars, end_date cast back to a date</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:13 PDT</t>
-        </is>
-      </c>
+      <c r="D236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -5652,11 +4716,7 @@
           <t>Phase 2 staging (paid media: Google Search): ad groups; cpc_bid_micros cast back to a number (always empty -- automated bidding)</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:13 PDT</t>
-        </is>
-      </c>
+      <c r="D237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -5674,11 +4734,7 @@
           <t>Phase 2 staging (paid media: Google Search): ad-group-day performance with combined ad_group_day_id key, cost converted from micros to dollars, ctr_fraction. The keyword table rolled up -- never add the two together</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:13 PDT</t>
-        </is>
-      </c>
+      <c r="D238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -5696,11 +4752,7 @@
           <t>Phase 2 staging (paid media: Google Search): keyword-day performance with combined keyword_day_id key, cost converted from micros to dollars, ctr_fraction</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:13 PDT</t>
-        </is>
-      </c>
+      <c r="D239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -5718,11 +4770,7 @@
           <t>Updated: tests for the 4 Google Search staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -5740,11 +4788,7 @@
           <t>Phase 2 staging (paid media: YouTube): campaigns with customer_id renamed google_ads_account_id (the ad account, not a Kinetic customer), budgets in micros and dollars</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:14 PDT</t>
-        </is>
-      </c>
+      <c r="D241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -5762,11 +4806,7 @@
           <t>Phase 2 staging (paid media: YouTube): 1:1 pass-through of youtube_ad_groups</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:14 PDT</t>
-        </is>
-      </c>
+      <c r="D242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -5784,11 +4824,7 @@
           <t>Phase 2 staging (paid media: YouTube): ad-group-day performance with combined ad_group_day_id key, cost and cost-per-view converted from micros to dollars, video_view_rate_fraction</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:14 PDT</t>
-        </is>
-      </c>
+      <c r="D243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -5806,11 +4842,7 @@
           <t>Updated: tests for the 3 YouTube staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -5828,11 +4860,7 @@
           <t>Phase 2 staging (paid media: DV360): insertion orders with budget_micros named monthly_budget_* (it's a monthly budget), end_date cast back to a date; flags the flat-budget-vs-growing-spend known issue</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:27 PDT</t>
-        </is>
-      </c>
+      <c r="D245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -5850,11 +4878,7 @@
           <t>Phase 2 staging (paid media: DV360): 1:1 pass-through of dv360_line_items</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:19 PDT</t>
-        </is>
-      </c>
+      <c r="D246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -5872,11 +4896,7 @@
           <t>Phase 2 staging (paid media: DV360): line-item x day x exchange x environment performance with combined line_item_day_slice_id key, micros converted to dollars, ctr_fraction</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:19 PDT</t>
-        </is>
-      </c>
+      <c r="D247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -5894,11 +4914,7 @@
           <t>Updated: tests for the 3 DV360 staging models, incl. accepted_values on exchange and environment -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -5916,11 +4932,7 @@
           <t>Updated 2026-09-29: every evergreen ad budget on all 6 platforms is now the campaign's CURRENT budget, sized from realized spend (weekly average &lt;= budget, no day &gt; 1.75x; DV360 monthly &gt;= highest month). The old flat 'typical day' budgets let later months spend up to ~20x the stored budget</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:23 PDT</t>
-        </is>
-      </c>
+      <c r="D249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -5938,11 +4950,7 @@
           <t>Regenerated 2026-09-29: evergreen daily_budget values updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -5960,11 +4968,7 @@
           <t>Regenerated 2026-09-29: campaign_budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -5982,11 +4986,7 @@
           <t>Regenerated 2026-09-29: evergreen campaign_budget_micros updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -6004,11 +5004,7 @@
           <t>Regenerated 2026-09-29: monthly budget_micros updated to current budgets (only that column changed)</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -6026,11 +5022,7 @@
           <t>Regenerated 2026-09-29: evergreen daily_budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -6048,11 +5040,7 @@
           <t>Regenerated 2026-09-29: BUDGET_MODE_DAY budget_micro updated to current budgets (only that column, only the 4 evergreen rows changed)</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:24 PDT</t>
-        </is>
-      </c>
+      <c r="D255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -6070,11 +5058,7 @@
           <t>Updated 2026-09-29: new Check 8 -- spend vs stored budget for every campaign on all 6 platforms (weekly/daily limits for daily budgets, monthly for DV360, total for holiday flights)</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:30 PDT</t>
-        </is>
-      </c>
+      <c r="D256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -6092,11 +5076,7 @@
           <t>Updated: budget known-issue note replaced -- budgets are now current budgets</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:27 PDT</t>
-        </is>
-      </c>
+      <c r="D257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -6114,11 +5094,7 @@
           <t>Updated 2026-09-29: new cap_flight_at_budget() -- rescales a holiday flight's days so it never spends past its lifetime budget, replaying the same random rates so every other row is unchanged</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -6136,11 +5112,7 @@
           <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -6158,11 +5130,7 @@
           <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -6180,11 +5148,7 @@
           <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget()</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -6202,11 +5166,7 @@
           <t>Updated 2026-09-29: holiday flights capped at their lifetime budget via cap_flight_at_budget() (no-op today -- all YouTube flights were already under budget)</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -6224,11 +5184,7 @@
           <t>Regenerated 2026-09-29: the 2023 and 2024 holiday flights (38 rows) trimmed to spend exactly their lifetime budget; every other row identical</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -6246,11 +5202,7 @@
           <t>Regenerated 2026-09-29: re-derived from the trimmed insights rows -- only the 2023/2024 holiday flights' action rows changed (one initiate_checkout row on 2024-11-15 dropped to zero and is no longer emitted)</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -6268,11 +5220,7 @@
           <t>Regenerated 2026-09-29: the 2024 holiday flight (19 rows) trimmed to spend exactly its lifetime budget; every other row identical</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -6290,11 +5238,7 @@
           <t>Regenerated 2026-09-29: the 2023/2024/2025 holiday flights (56 rows) trimmed to spend exactly their lifetime budgets; every other row identical</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:29 PDT</t>
-        </is>
-      </c>
+      <c r="D266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -6312,11 +5256,7 @@
           <t>Updated 2026-09-29: added Check 8 (spend vs stored budget) with both fixes and results</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:54 PDT</t>
-        </is>
-      </c>
+      <c r="D267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -6334,11 +5274,7 @@
           <t>Updated 2026-09-29: Check 8's flight limit tightened from 1.05x to 1.0x now that flights are capped</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 13:30 PDT</t>
-        </is>
-      </c>
+      <c r="D268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -6356,11 +5292,7 @@
           <t>Phase 2 staging (paid media: Snap): campaigns with ad_account_id renamed snap_ad_account_id, current budgets in micros and dollars</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:53 PDT</t>
-        </is>
-      </c>
+      <c r="D269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -6378,11 +5310,7 @@
           <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ad_squads (Snap's ad set / ad group level)</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:53 PDT</t>
-        </is>
-      </c>
+      <c r="D270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -6400,11 +5328,7 @@
           <t>Phase 2 staging (paid media: Snap): 1:1 pass-through of snap_ads</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:53 PDT</t>
-        </is>
-      </c>
+      <c r="D271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -6422,11 +5346,7 @@
           <t>Phase 2 staging (paid media: Snap): ad-day stats with combined ad_day_id key, spend in micros and dollars; documents swipes as Snap's clicks</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:53 PDT</t>
-        </is>
-      </c>
+      <c r="D272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -6444,11 +5364,7 @@
           <t>Updated: tests for the 4 Snap staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -6466,11 +5382,7 @@
           <t>Phase 2 staging (paid media: TikTok): campaigns with the single budget split into daily_budget_usd / lifetime_budget_usd by budget_mode (matching the other platforms), advertiser_id renamed tiktok_advertiser_id</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:57 PDT</t>
-        </is>
-      </c>
+      <c r="D274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -6488,11 +5400,7 @@
           <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_adgroups</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:57 PDT</t>
-        </is>
-      </c>
+      <c r="D275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -6510,11 +5418,7 @@
           <t>Phase 2 staging (paid media: TikTok): 1:1 pass-through of tiktok_ads</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:57 PDT</t>
-        </is>
-      </c>
+      <c r="D276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -6532,11 +5436,7 @@
           <t>Phase 2 staging (paid media: TikTok): ad-day reports with combined ad_day_id key, spend and CPM in micros and dollars, ctr_fraction</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:57 PDT</t>
-        </is>
-      </c>
+      <c r="D277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -6554,11 +5454,7 @@
           <t>Phase 2 staging (final table, 47 of 47): product variants with variant_option, price_adjustment_usd</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 16:08 PDT</t>
-        </is>
-      </c>
+      <c r="D278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -6576,11 +5472,7 @@
           <t>Handoff note for starting a new chat/project: status, open decisions, prior decisions, pitfalls</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:29 PDT</t>
-        </is>
-      </c>
+      <c r="D279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -6598,11 +5490,7 @@
           <t>Updated: tests for the 4 TikTok staging models -- all hand-verified against live data first</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:11 PDT</t>
-        </is>
-      </c>
+      <c r="D280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -6620,11 +5508,7 @@
           <t>Intermediate model: one row per Braze email or push event in one shape, customer resolved via Braze id or email match (written and hand-verified; needs dbt build)</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:03 PDT</t>
-        </is>
-      </c>
+      <c r="D281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -6642,11 +5526,7 @@
           <t>dbt test: unified event count equals email + push event counts</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:03 PDT</t>
-        </is>
-      </c>
+      <c r="D282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -6664,11 +5544,7 @@
           <t>dbt test: customer_id is null exactly when a messaging event is unresolved</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:03 PDT</t>
-        </is>
-      </c>
+      <c r="D283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -6686,11 +5562,7 @@
           <t>Overnight run report: commands to run first, assumed decisions, done/blocked units, proposed playbook wording</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 06:53 PDT</t>
-        </is>
-      </c>
+      <c r="D284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -6708,11 +5580,7 @@
           <t>Intermediate model: one row per ad platform per day, spend/impressions/clicks/conversions in USD (written and hand-verified; needs dbt build)</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:05 PDT</t>
-        </is>
-      </c>
+      <c r="D285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -6730,11 +5598,7 @@
           <t>dbt test: platform-day spend total equals the six source spend totals</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:05 PDT</t>
-        </is>
-      </c>
+      <c r="D286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -6752,11 +5616,7 @@
           <t>dbt test: no missing days per platform</t>
         </is>
       </c>
-      <c r="D287" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:05 PDT</t>
-        </is>
-      </c>
+      <c r="D287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -6774,11 +5634,7 @@
           <t>Intermediate model: one row, the last date the subscription/invoice data covers (shared by MRR and subscriber-movement marts) (written; needs dbt build)</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:07 PDT</t>
-        </is>
-      </c>
+      <c r="D288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -6796,11 +5652,7 @@
           <t>Phase 4 mart (CEO): new/returning/churned/net-new/active paying subscribers by month (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:07 PDT</t>
-        </is>
-      </c>
+      <c r="D289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -6818,11 +5670,7 @@
           <t>dbt test: end-of-month active = previous + new - churned</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:07 PDT</t>
-        </is>
-      </c>
+      <c r="D290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -6840,11 +5688,7 @@
           <t>dbt test: total new and churned match the paid-periods source</t>
         </is>
       </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:07 PDT</t>
-        </is>
-      </c>
+      <c r="D291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -6862,11 +5706,7 @@
           <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:08 PDT</t>
-        </is>
-      </c>
+      <c r="D292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -6884,11 +5724,7 @@
           <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:08 PDT</t>
-        </is>
-      </c>
+      <c r="D293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -6906,11 +5742,7 @@
           <t>dbt test: monthly paid media spend equals daily total</t>
         </is>
       </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:08 PDT</t>
-        </is>
-      </c>
+      <c r="D294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -6928,11 +5760,7 @@
           <t>dbt test: CAC mart spend equals total paid media spend</t>
         </is>
       </c>
-      <c r="D295" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:08 PDT</t>
-        </is>
-      </c>
+      <c r="D295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -6950,11 +5778,7 @@
           <t>DRAFT Phase 6 semantic layer (MetricFlow semantic models + metrics) for the marts built so far; unvalidated, outside model-paths</t>
         </is>
       </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:13 PDT</t>
-        </is>
-      </c>
+      <c r="D296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -6972,11 +5796,7 @@
           <t>DRAFT Phase 6 validation set: mf query commands with expected values from hand SQL (not yet run)</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:13 PDT</t>
-        </is>
-      </c>
+      <c r="D297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -6994,11 +5814,7 @@
           <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules (not reviewed by data owner)</t>
         </is>
       </c>
-      <c r="D298" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 22:13 PDT</t>
-        </is>
-      </c>
+      <c r="D298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -7016,11 +5832,7 @@
           <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
         </is>
       </c>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:17 PDT</t>
-        </is>
-      </c>
+      <c r="D299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -7038,11 +5850,7 @@
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 08:34 PDT</t>
-        </is>
-      </c>
+      <c r="D300" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:55 PDT</t>
+          <t>2026-09-30 08:57 PDT</t>
         </is>
       </c>
     </row>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D300"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 08:57 PDT</t>
+          <t>2026-09-30 09:56 PDT</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>dbt/drafts/semantic_layer_DRAFT.yml</t>
+          <t>dbt/models/marts/_semantic_layer.yml</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>DRAFT Phase 6 semantic layer (MetricFlow semantic models + metrics) for the marts built so far; unvalidated, outside model-paths</t>
+          <t>Phase 6 semantic layer (MetricFlow): 5 semantic models, 25 metrics on the marts; validated 2026-09-30</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr"/>
@@ -5783,17 +5783,17 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>docs/semantic_layer_validation_DRAFT.md</t>
+          <t>dbt/models/marts/metricflow_time_spine.sql</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>DRAFT Phase 6 validation set: mf query commands with expected values from hand SQL (not yet run)</t>
+          <t>Phase 6 calendar table (one row per day, ends at the data's last day) required by MetricFlow</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr"/>
@@ -5801,7 +5801,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>docs/kinetic_skill_DRAFT.md</t>
+          <t>docs/semantic_layer_validation.md</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules (not reviewed by data owner)</t>
+          <t>Phase 6 validation set: 10 mf query commands with expected and returned values (all match, run 2026-09-30)</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr"/>
@@ -5819,7 +5819,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>docs/metrics_glossary.md</t>
+          <t>docs/kinetic_skill_DRAFT.md</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules (not reviewed by data owner)</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>
@@ -5837,20 +5837,38 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
+          <t>docs/metrics_glossary.md</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B300" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr"/>
+      <c r="D301" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:56 PDT</t>
+          <t>2026-09-30 10:19 PDT</t>
         </is>
       </c>
     </row>
@@ -5855,20 +5855,38 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
+          <t>scripts/md_select.py</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C301" s="3" t="inlineStr">
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr"/>
+      <c r="D302" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:19 PDT</t>
+          <t>2026-09-30 10:23 PDT</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules (not reviewed by data owner)</t>
+          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); in Ben's review</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:23 PDT</t>
+          <t>2026-09-30 10:30 PDT</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>docs/kinetic_skill_DRAFT.md</t>
+          <t>docs/kinetic_skill.md</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>DRAFT Phase 7 Skill: which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); in Ben's review</t>
+          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); in Ben's review</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D302"/>
+  <dimension ref="A1:D303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30 PDT</t>
+          <t>2026-09-30 10:36 PDT</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>docs/metrics_glossary.md</t>
+          <t>docs/phase8_pilot_scope.md</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+          <t>Phase 8 pilot scope (DRAFT, Ben reviewing): CMO paid-media check, 6 test questions with live-checked answers, guardrails, pass criteria, open setup decisions</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr"/>
@@ -5855,17 +5855,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>scripts/md_select.py</t>
+          <t>docs/metrics_glossary.md</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr"/>
@@ -5873,20 +5873,38 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
+          <t>scripts/md_select.py</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B302" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C302" s="3" t="inlineStr">
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D302" s="2" t="inlineStr"/>
+      <c r="D303" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D303"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:36 PDT</t>
+          <t>2026-09-30 10:42 PDT</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); in Ben's review</t>
+          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); v1.1 adds a read-only (SELECT only) rule for the Phase 8 pilot</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Phase 8 pilot scope (DRAFT, Ben reviewing): CMO paid-media check, 6 test questions with live-checked answers, guardrails, pass criteria, open setup decisions</t>
+          <t>Phase 8 pilot scope (approved 2026-09-30): CMO paid-media check, 6 test questions with live-checked answers, pass criteria, Ben's setup decisions (dev schema, claude.ai, write tool off, pilot log)</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>docs/metrics_glossary.md</t>
+          <t>docs/phase8_pilot_log.md</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+          <t>Phase 8 pilot log: one graded row per question asked to the pilot agent (verdict, cited or not, notes)</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr"/>
@@ -5873,17 +5873,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>scripts/md_select.py</t>
+          <t>docs/metrics_glossary.md</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr"/>
@@ -5891,20 +5891,38 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
+          <t>scripts/md_select.py</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C303" s="3" t="inlineStr">
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D303" s="2" t="inlineStr"/>
+      <c r="D304" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:42 PDT</t>
+          <t>2026-09-30 11:28 PDT</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_paid_media_monthly.sql</t>
+          <t>dbt/models/marts/mart_messaging_monthly.sql</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
+          <t>dbt mart: email and push by channel x campaign type x month (sends, bounces, delivered, opens, clicks, unsubscribes and rates); hand-validated, built 12/12</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr"/>
@@ -5711,7 +5711,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_acquisition_efficiency_monthly.sql</t>
+          <t>dbt/tests/assert_mart_messaging_monthly_totals_match_events.sql</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
+          <t>dbt test: messaging mart totals per channel equal the events in int_messaging_events</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_paid_media_monthly_spend_matches_daily.sql</t>
+          <t>dbt/tests/assert_mart_messaging_monthly_identity.sql</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>dbt test: monthly paid media spend equals daily total</t>
+          <t>dbt test: messaging funnel logic (delivered = sends - bounces, opens &lt;= delivered, clicks &lt;= opens, rates in 0-1)</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_acquisition_efficiency_monthly_spend_matches_daily.sql</t>
+          <t>dbt/models/marts/mart_paid_media_monthly.sql</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>dbt test: CAC mart spend equals total paid media spend</t>
+          <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr"/>
@@ -5765,17 +5765,17 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/_semantic_layer.yml</t>
+          <t>dbt/models/marts/mart_acquisition_efficiency_monthly.sql</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 semantic layer (MetricFlow): 5 semantic models, 25 metrics on the marts; validated 2026-09-30</t>
+          <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr"/>
@@ -5783,7 +5783,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/metricflow_time_spine.sql</t>
+          <t>dbt/tests/assert_mart_paid_media_monthly_spend_matches_daily.sql</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 calendar table (one row per day, ends at the data's last day) required by MetricFlow</t>
+          <t>dbt test: monthly paid media spend equals daily total</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr"/>
@@ -5801,17 +5801,17 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>docs/semantic_layer_validation.md</t>
+          <t>dbt/tests/assert_mart_acquisition_efficiency_monthly_spend_matches_daily.sql</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 validation set: 10 mf query commands with expected and returned values (all match, run 2026-09-30)</t>
+          <t>dbt test: CAC mart spend equals total paid media spend</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr"/>
@@ -5819,17 +5819,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>docs/kinetic_skill.md</t>
+          <t>dbt/models/marts/_semantic_layer.yml</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); v1.1 adds a read-only (SELECT only) rule for the Phase 8 pilot</t>
+          <t>Phase 6 semantic layer (MetricFlow): 5 semantic models, 25 metrics on the marts; validated 2026-09-30</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>
@@ -5837,17 +5837,17 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>docs/phase8_pilot_scope.md</t>
+          <t>dbt/models/marts/metricflow_time_spine.sql</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Phase 8 pilot scope (approved 2026-09-30): CMO paid-media check, 6 test questions with live-checked answers, pass criteria, Ben's setup decisions (dev schema, claude.ai, write tool off, pilot log)</t>
+          <t>Phase 6 calendar table (one row per day, ends at the data's last day) required by MetricFlow</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>docs/phase8_pilot_log.md</t>
+          <t>docs/semantic_layer_validation.md</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>Phase 8 pilot log: one graded row per question asked to the pilot agent (verdict, cited or not, notes)</t>
+          <t>Phase 6 validation set: 10 mf query commands with expected and returned values (all match, run 2026-09-30)</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr"/>
@@ -5873,7 +5873,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>docs/metrics_glossary.md</t>
+          <t>docs/kinetic_skill.md</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); v1.1 adds a read-only (SELECT only) rule for the Phase 8 pilot</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr"/>
@@ -5891,17 +5891,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>scripts/md_select.py</t>
+          <t>docs/phase8_pilot_scope.md</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+          <t>Phase 8 pilot scope (approved 2026-09-30): CMO paid-media check, 6 test questions with live-checked answers, pass criteria, Ben's setup decisions (dev schema, claude.ai, write tool off, pilot log)</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr"/>
@@ -5909,20 +5909,92 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
+          <t>docs/phase8_pilot_log.md</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>Phase 8 pilot log: one graded row per question asked to the pilot agent (verdict, cited or not, notes)</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>docs/metrics_glossary.md</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>scripts/md_env.sh</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONLY dbt or mf (MetricFlow) from dbt/ with the MotherDuck token loaded from ~/.zshrc (never printed), so no browser sign-in</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>scripts/md_select.py</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C304" s="3" t="inlineStr">
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D304" s="2" t="inlineStr"/>
+      <c r="D308" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D308"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 11:28 PDT</t>
+          <t>2026-09-30 11:29 PDT</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_messaging_monthly.sql</t>
+          <t>dbt/models/marts/mart_traffic_monthly.sql</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>dbt mart: email and push by channel x campaign type x month (sends, bounces, delivered, opens, clicks, unsubscribes and rates); hand-validated, built 12/12</t>
+          <t>dbt mart: web and app sessions by month x traffic source x landing page (sessions, known/anonymous, duration); hand-validated, built 11/11</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr"/>
@@ -5711,7 +5711,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_messaging_monthly_totals_match_events.sql</t>
+          <t>dbt/tests/assert_mart_traffic_monthly_totals_match_sessions.sql</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>dbt test: messaging mart totals per channel equal the events in int_messaging_events</t>
+          <t>dbt test: traffic mart sessions and seconds equal int_sessions_unified</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr"/>
@@ -5729,7 +5729,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_messaging_monthly_identity.sql</t>
+          <t>dbt/tests/assert_mart_traffic_monthly_identity.sql</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>dbt test: messaging funnel logic (delivered = sends - bounces, opens &lt;= delivered, clicks &lt;= opens, rates in 0-1)</t>
+          <t>dbt test: traffic mart known + anonymous = sessions, rates in 0-1</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr"/>
@@ -5747,7 +5747,7 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_paid_media_monthly.sql</t>
+          <t>dbt/models/marts/mart_messaging_monthly.sql</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
+          <t>dbt mart: email and push by channel x campaign type x month (sends, bounces, delivered, opens, clicks, unsubscribes and rates); hand-validated, built 12/12</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/mart_acquisition_efficiency_monthly.sql</t>
+          <t>dbt/tests/assert_mart_messaging_monthly_totals_match_events.sql</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
+          <t>dbt test: messaging mart totals per channel equal the events in int_messaging_events</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr"/>
@@ -5783,7 +5783,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_paid_media_monthly_spend_matches_daily.sql</t>
+          <t>dbt/tests/assert_mart_messaging_monthly_identity.sql</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>dbt test: monthly paid media spend equals daily total</t>
+          <t>dbt test: messaging funnel logic (delivered = sends - bounces, opens &lt;= delivered, clicks &lt;= opens, rates in 0-1)</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr"/>
@@ -5801,7 +5801,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>dbt/tests/assert_mart_acquisition_efficiency_monthly_spend_matches_daily.sql</t>
+          <t>dbt/models/marts/mart_paid_media_monthly.sql</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>dbt test: CAC mart spend equals total paid media spend</t>
+          <t>Phase 4 mart (Performance Marketing/CMO): spend, clicks, platform-reported conversions and ratios by platform by month (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr"/>
@@ -5819,17 +5819,17 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/_semantic_layer.yml</t>
+          <t>dbt/models/marts/mart_acquisition_efficiency_monthly.sql</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Config</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 semantic layer (MetricFlow): 5 semantic models, 25 metrics on the marts; validated 2026-09-30</t>
+          <t>Phase 4 mart (CEO/CFO): blended CAC by month = paid spend / first-time paying subscribers (written and hand-validated; needs dbt build)</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>dbt/models/marts/metricflow_time_spine.sql</t>
+          <t>dbt/tests/assert_mart_paid_media_monthly_spend_matches_daily.sql</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 calendar table (one row per day, ends at the data's last day) required by MetricFlow</t>
+          <t>dbt test: monthly paid media spend equals daily total</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr"/>
@@ -5855,17 +5855,17 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>docs/semantic_layer_validation.md</t>
+          <t>dbt/tests/assert_mart_acquisition_efficiency_monthly_spend_matches_daily.sql</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>Phase 6 validation set: 10 mf query commands with expected and returned values (all match, run 2026-09-30)</t>
+          <t>dbt test: CAC mart spend equals total paid media spend</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr"/>
@@ -5873,17 +5873,17 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>docs/kinetic_skill.md</t>
+          <t>dbt/models/marts/_semantic_layer.yml</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); v1.1 adds a read-only (SELECT only) rule for the Phase 8 pilot</t>
+          <t>Phase 6 semantic layer (MetricFlow): 5 semantic models, 25 metrics on the marts; validated 2026-09-30</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr"/>
@@ -5891,17 +5891,17 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>docs/phase8_pilot_scope.md</t>
+          <t>dbt/models/marts/metricflow_time_spine.sql</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Doc</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>Phase 8 pilot scope (approved 2026-09-30): CMO paid-media check, 6 test questions with live-checked answers, pass criteria, Ben's setup decisions (dev schema, claude.ai, write tool off, pilot log)</t>
+          <t>Phase 6 calendar table (one row per day, ends at the data's last day) required by MetricFlow</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr"/>
@@ -5909,7 +5909,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>docs/phase8_pilot_log.md</t>
+          <t>docs/semantic_layer_validation.md</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>Phase 8 pilot log: one graded row per question asked to the pilot agent (verdict, cited or not, notes)</t>
+          <t>Phase 6 validation set: 10 mf query commands with expected and returned values (all match, run 2026-09-30)</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr"/>
@@ -5927,7 +5927,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>docs/metrics_glossary.md</t>
+          <t>docs/kinetic_skill.md</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+          <t>Phase 7 Skill (signed off 2026-09-30): which mart answers which question, Phase 5 caveats as instructions, 'I don't have this data' rules; v2 adds how to get the numbers (SQL on marts, or MetricFlow metrics); v1.1 adds a read-only (SELECT only) rule for the Phase 8 pilot</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr"/>
@@ -5945,17 +5945,17 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>scripts/md_env.sh</t>
+          <t>docs/phase8_pilot_scope.md</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>Script: run ONLY dbt or mf (MetricFlow) from dbt/ with the MotherDuck token loaded from ~/.zshrc (never printed), so no browser sign-in</t>
+          <t>Phase 8 pilot scope (approved 2026-09-30): CMO paid-media check, 6 test questions with live-checked answers, pass criteria, Ben's setup decisions (dev schema, claude.ai, write tool off, pilot log)</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr"/>
@@ -5963,17 +5963,17 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>scripts/md_select.py</t>
+          <t>docs/phase8_pilot_log.md</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+          <t>Phase 8 pilot log: one graded row per question asked to the pilot agent (verdict, cited or not, notes)</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr"/>
@@ -5981,20 +5981,74 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
+          <t>docs/metrics_glossary.md</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>Phase 5 metrics glossary: plain-language definition of every mart metric, its grain, source and what it does NOT mean</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>scripts/md_env.sh</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONLY dbt or mf (MetricFlow) from dbt/ with the MotherDuck token loaded from ~/.zshrc (never printed), so no browser sign-in</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>scripts/md_select.py</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>Script: run ONE read-only SQL statement (SELECT/WITH/DESCRIBE...) on MotherDuck kinetic; refuses writes/DDL; loads the token itself, never prints it</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
           <t>scripts/rebuild_docs_branch.sh</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C308" s="3" t="inlineStr">
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
         <is>
           <t>Script: rebuild the gh-pages branch (published dbt docs site) from dbt/target as one fast-forward commit; refuses local paths/tokens</t>
         </is>
       </c>
-      <c r="D308" s="2" t="inlineStr"/>
+      <c r="D311" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/File_Manifest.xlsx
+++ b/File_Manifest.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 11:29 PDT</t>
+          <t>2026-09-30 11:34 PDT</t>
         </is>
       </c>
     </row>
